--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -120,9 +120,6 @@
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
@@ -135,19 +132,16 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
@@ -156,13 +150,10 @@
     <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
@@ -172,16 +163,13 @@
 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
@@ -194,7 +182,22 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -1456,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1509,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1553,7 +1556,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1606,7 +1609,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1659,7 +1662,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1712,7 +1715,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1721,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1765,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1774,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -1818,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1827,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1880,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1933,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -1986,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2039,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2092,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2145,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -2198,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2251,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2304,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2357,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2410,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2463,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -2516,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2569,7 +2572,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2622,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2675,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2728,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2781,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -2825,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
@@ -2834,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2878,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -2887,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -2931,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -2940,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -2984,7 +2987,7 @@
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -2993,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -3037,7 +3040,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -3046,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3090,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -3099,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -3152,7 +3155,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3205,7 +3208,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3258,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3311,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3364,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3417,7 +3420,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3470,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3523,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3576,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3629,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3682,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3735,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3788,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3841,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3894,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3947,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -4000,7 +4003,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -4053,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4097,7 +4100,7 @@
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I68" t="n">
         <v>3</v>
@@ -4106,7 +4109,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4150,7 +4153,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I69" t="n">
         <v>3</v>
@@ -4159,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4203,7 +4206,7 @@
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I70" t="n">
         <v>3</v>
@@ -4212,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4256,7 +4259,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -4265,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4309,7 +4312,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I72" t="n">
         <v>3</v>
@@ -4318,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4362,7 +4365,7 @@
         <v>2</v>
       </c>
       <c r="H73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I73" t="n">
         <v>3</v>
@@ -4371,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4424,7 +4427,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4477,7 +4480,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4530,7 +4533,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4583,13 +4586,13 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
@@ -4636,13 +4639,13 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
@@ -4689,13 +4692,13 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
@@ -4742,7 +4745,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4795,7 +4798,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4848,7 +4851,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4901,13 +4904,13 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N83" t="s">
         <v>32</v>
@@ -4954,13 +4957,13 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N84" t="s">
         <v>32</v>
@@ -5007,13 +5010,13 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N85" t="s">
         <v>32</v>
@@ -5060,7 +5063,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5113,7 +5116,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5166,7 +5169,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5219,13 +5222,13 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
@@ -5272,13 +5275,13 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
@@ -5325,13 +5328,13 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
@@ -5351,7 +5354,7 @@
         <v>184</v>
       </c>
       <c r="B92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="s">
         <v>17</v>
@@ -5369,7 +5372,7 @@
         <v>2</v>
       </c>
       <c r="H92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I92" t="n">
         <v>4</v>
@@ -5378,7 +5381,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5404,7 +5407,7 @@
         <v>185</v>
       </c>
       <c r="B93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="s">
         <v>17</v>
@@ -5422,7 +5425,7 @@
         <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I93" t="n">
         <v>4</v>
@@ -5431,7 +5434,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5457,7 +5460,7 @@
         <v>186</v>
       </c>
       <c r="B94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
@@ -5475,7 +5478,7 @@
         <v>2</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I94" t="n">
         <v>4</v>
@@ -5484,7 +5487,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5528,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
@@ -5537,13 +5540,13 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N95" t="s">
         <v>32</v>
@@ -5581,7 +5584,7 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
@@ -5590,13 +5593,13 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N96" t="s">
         <v>32</v>
@@ -5634,7 +5637,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
@@ -5643,13 +5646,13 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
@@ -5696,7 +5699,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -5749,7 +5752,7 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
@@ -5802,7 +5805,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
@@ -5855,13 +5858,13 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N101" t="s">
         <v>26</v>
@@ -5908,13 +5911,13 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N102" t="s">
         <v>26</v>
@@ -5961,13 +5964,13 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N103" t="s">
         <v>26</v>
@@ -6014,7 +6017,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6067,7 +6070,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6120,7 +6123,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6173,13 +6176,13 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
@@ -6226,13 +6229,13 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
@@ -6279,13 +6282,13 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N109" t="s">
         <v>32</v>
@@ -6332,7 +6335,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -6385,7 +6388,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
@@ -6438,7 +6441,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
@@ -6491,13 +6494,13 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N113" t="s">
         <v>26</v>
@@ -6544,13 +6547,13 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N114" t="s">
         <v>26</v>
@@ -6597,13 +6600,13 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N115" t="s">
         <v>26</v>
@@ -6623,7 +6626,7 @@
         <v>232</v>
       </c>
       <c r="B116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="s">
         <v>17</v>
@@ -6641,7 +6644,7 @@
         <v>2</v>
       </c>
       <c r="H116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I116" t="n">
         <v>5</v>
@@ -6650,7 +6653,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6676,7 +6679,7 @@
         <v>233</v>
       </c>
       <c r="B117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" t="s">
         <v>17</v>
@@ -6694,7 +6697,7 @@
         <v>2</v>
       </c>
       <c r="H117" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I117" t="n">
         <v>5</v>
@@ -6703,7 +6706,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6729,7 +6732,7 @@
         <v>234</v>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="s">
         <v>17</v>
@@ -6747,7 +6750,7 @@
         <v>2</v>
       </c>
       <c r="H118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I118" t="n">
         <v>5</v>
@@ -6756,7 +6759,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6800,7 +6803,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -6809,13 +6812,13 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
@@ -6853,7 +6856,7 @@
         <v>2</v>
       </c>
       <c r="H120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -6862,13 +6865,13 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
@@ -6906,7 +6909,7 @@
         <v>2</v>
       </c>
       <c r="H121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -6915,13 +6918,13 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
@@ -6968,13 +6971,13 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
@@ -7021,13 +7024,13 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
@@ -7074,13 +7077,13 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
@@ -7127,13 +7130,13 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N125" t="s">
         <v>26</v>
@@ -7180,13 +7183,13 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N126" t="s">
         <v>26</v>
@@ -7233,13 +7236,13 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N127" t="s">
         <v>26</v>
@@ -7286,13 +7289,13 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
@@ -7339,13 +7342,13 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
@@ -7392,13 +7395,13 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
@@ -7445,13 +7448,13 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N131" t="s">
         <v>32</v>
@@ -7498,13 +7501,13 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N132" t="s">
         <v>32</v>
@@ -7551,13 +7554,13 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N133" t="s">
         <v>32</v>
@@ -7604,13 +7607,13 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
@@ -7657,13 +7660,13 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
@@ -7710,13 +7713,13 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
@@ -7763,13 +7766,13 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N137" t="s">
         <v>26</v>
@@ -7816,13 +7819,13 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N138" t="s">
         <v>26</v>
@@ -7869,13 +7872,13 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N139" t="s">
         <v>26</v>
@@ -7913,7 +7916,7 @@
         <v>2</v>
       </c>
       <c r="H140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I140" t="n">
         <v>6</v>
@@ -7922,13 +7925,13 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
@@ -7966,7 +7969,7 @@
         <v>2</v>
       </c>
       <c r="H141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I141" t="n">
         <v>6</v>
@@ -7975,13 +7978,13 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
@@ -8019,7 +8022,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I142" t="n">
         <v>6</v>
@@ -8028,13 +8031,13 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
@@ -8072,7 +8075,7 @@
         <v>2</v>
       </c>
       <c r="H143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
@@ -8081,13 +8084,13 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N143" t="s">
         <v>32</v>
@@ -8125,7 +8128,7 @@
         <v>2</v>
       </c>
       <c r="H144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I144" t="n">
         <v>6</v>
@@ -8134,13 +8137,13 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N144" t="s">
         <v>32</v>
@@ -8178,7 +8181,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I145" t="n">
         <v>6</v>
@@ -8187,13 +8190,13 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N145" t="s">
         <v>32</v>
@@ -8206,6 +8209,3678 @@
       </c>
       <c r="Q145" t="n">
         <v>702</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>292</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="s">
+        <v>54</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="s">
+        <v>55</v>
+      </c>
+      <c r="N146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O146" t="n">
+        <v>11</v>
+      </c>
+      <c r="P146" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>293</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>54</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>55</v>
+      </c>
+      <c r="N147" t="s">
+        <v>22</v>
+      </c>
+      <c r="O147" t="n">
+        <v>11</v>
+      </c>
+      <c r="P147" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>294</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>54</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="s">
+        <v>55</v>
+      </c>
+      <c r="N148" t="s">
+        <v>22</v>
+      </c>
+      <c r="O148" t="n">
+        <v>11</v>
+      </c>
+      <c r="P148" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>298</v>
+      </c>
+      <c r="B149" t="b">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>56</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>25</v>
+      </c>
+      <c r="N149" t="s">
+        <v>26</v>
+      </c>
+      <c r="O149"/>
+      <c r="P149" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q149"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>299</v>
+      </c>
+      <c r="B150" t="b">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>56</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="s">
+        <v>25</v>
+      </c>
+      <c r="N150" t="s">
+        <v>26</v>
+      </c>
+      <c r="O150"/>
+      <c r="P150" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q150"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>300</v>
+      </c>
+      <c r="B151" t="b">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>56</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="s">
+        <v>25</v>
+      </c>
+      <c r="N151" t="s">
+        <v>26</v>
+      </c>
+      <c r="O151"/>
+      <c r="P151" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q151"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>304</v>
+      </c>
+      <c r="B152" t="b">
+        <v>1</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" t="n">
+        <v>7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>54</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="s">
+        <v>28</v>
+      </c>
+      <c r="N152" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152"/>
+      <c r="P152" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q152"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>305</v>
+      </c>
+      <c r="B153" t="b">
+        <v>1</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I153" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>54</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" t="s">
+        <v>29</v>
+      </c>
+      <c r="O153"/>
+      <c r="P153" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q153"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>306</v>
+      </c>
+      <c r="B154" t="b">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>54</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O154"/>
+      <c r="P154" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q154"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>310</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>30</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>56</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="s">
+        <v>57</v>
+      </c>
+      <c r="N155" t="s">
+        <v>32</v>
+      </c>
+      <c r="O155" t="n">
+        <v>7</v>
+      </c>
+      <c r="P155" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>311</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>30</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>56</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="s">
+        <v>57</v>
+      </c>
+      <c r="N156" t="s">
+        <v>32</v>
+      </c>
+      <c r="O156" t="n">
+        <v>7</v>
+      </c>
+      <c r="P156" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>312</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>30</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>56</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" t="s">
+        <v>57</v>
+      </c>
+      <c r="N157" t="s">
+        <v>32</v>
+      </c>
+      <c r="O157" t="n">
+        <v>7</v>
+      </c>
+      <c r="P157" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>316</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="s">
+        <v>33</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="s">
+        <v>54</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>55</v>
+      </c>
+      <c r="N158" t="s">
+        <v>22</v>
+      </c>
+      <c r="O158" t="n">
+        <v>11</v>
+      </c>
+      <c r="P158" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>317</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="s">
+        <v>33</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>54</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="s">
+        <v>55</v>
+      </c>
+      <c r="N159" t="s">
+        <v>22</v>
+      </c>
+      <c r="O159" t="n">
+        <v>11</v>
+      </c>
+      <c r="P159" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>318</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>33</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>54</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="s">
+        <v>55</v>
+      </c>
+      <c r="N160" t="s">
+        <v>22</v>
+      </c>
+      <c r="O160" t="n">
+        <v>11</v>
+      </c>
+      <c r="P160" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>322</v>
+      </c>
+      <c r="B161" t="b">
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>56</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="s">
+        <v>25</v>
+      </c>
+      <c r="N161" t="s">
+        <v>26</v>
+      </c>
+      <c r="O161"/>
+      <c r="P161" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q161"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>323</v>
+      </c>
+      <c r="B162" t="b">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>34</v>
+      </c>
+      <c r="I162" t="n">
+        <v>7</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>56</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="s">
+        <v>25</v>
+      </c>
+      <c r="N162" t="s">
+        <v>26</v>
+      </c>
+      <c r="O162"/>
+      <c r="P162" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q162"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>324</v>
+      </c>
+      <c r="B163" t="b">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="s">
+        <v>34</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>56</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="s">
+        <v>25</v>
+      </c>
+      <c r="N163" t="s">
+        <v>26</v>
+      </c>
+      <c r="O163"/>
+      <c r="P163" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q163"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>328</v>
+      </c>
+      <c r="B164" t="b">
+        <v>1</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="s">
+        <v>35</v>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="s">
+        <v>54</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" t="s">
+        <v>29</v>
+      </c>
+      <c r="O164"/>
+      <c r="P164" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q164"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>329</v>
+      </c>
+      <c r="B165" t="b">
+        <v>1</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="s">
+        <v>35</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="s">
+        <v>54</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" t="s">
+        <v>29</v>
+      </c>
+      <c r="O165"/>
+      <c r="P165" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q165"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>330</v>
+      </c>
+      <c r="B166" t="b">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="s">
+        <v>35</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
+        <v>54</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" t="s">
+        <v>28</v>
+      </c>
+      <c r="N166" t="s">
+        <v>29</v>
+      </c>
+      <c r="O166"/>
+      <c r="P166" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q166"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>334</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="s">
+        <v>36</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="s">
+        <v>56</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="s">
+        <v>57</v>
+      </c>
+      <c r="N167" t="s">
+        <v>32</v>
+      </c>
+      <c r="O167" t="n">
+        <v>7</v>
+      </c>
+      <c r="P167" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>335</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
+        <v>36</v>
+      </c>
+      <c r="I168" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="s">
+        <v>56</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="s">
+        <v>57</v>
+      </c>
+      <c r="N168" t="s">
+        <v>32</v>
+      </c>
+      <c r="O168" t="n">
+        <v>7</v>
+      </c>
+      <c r="P168" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>336</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="s">
+        <v>36</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="s">
+        <v>56</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="s">
+        <v>57</v>
+      </c>
+      <c r="N169" t="s">
+        <v>32</v>
+      </c>
+      <c r="O169" t="n">
+        <v>7</v>
+      </c>
+      <c r="P169" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>340</v>
+      </c>
+      <c r="B170" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>19</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="s">
+        <v>58</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="s">
+        <v>55</v>
+      </c>
+      <c r="N170" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" t="n">
+        <v>11</v>
+      </c>
+      <c r="P170" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>341</v>
+      </c>
+      <c r="B171" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>58</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="s">
+        <v>55</v>
+      </c>
+      <c r="N171" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" t="n">
+        <v>11</v>
+      </c>
+      <c r="P171" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>342</v>
+      </c>
+      <c r="B172" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="s">
+        <v>58</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="s">
+        <v>55</v>
+      </c>
+      <c r="N172" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" t="n">
+        <v>11</v>
+      </c>
+      <c r="P172" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>346</v>
+      </c>
+      <c r="B173" t="b">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="s">
+        <v>56</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="s">
+        <v>25</v>
+      </c>
+      <c r="N173" t="s">
+        <v>26</v>
+      </c>
+      <c r="O173"/>
+      <c r="P173" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q173"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>347</v>
+      </c>
+      <c r="B174" t="b">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="s">
+        <v>56</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="s">
+        <v>25</v>
+      </c>
+      <c r="N174" t="s">
+        <v>26</v>
+      </c>
+      <c r="O174"/>
+      <c r="P174" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q174"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>348</v>
+      </c>
+      <c r="B175" t="b">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>18</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>56</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="s">
+        <v>25</v>
+      </c>
+      <c r="N175" t="s">
+        <v>26</v>
+      </c>
+      <c r="O175"/>
+      <c r="P175" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q175"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>352</v>
+      </c>
+      <c r="B176" t="b">
+        <v>1</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>27</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>58</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O176"/>
+      <c r="P176" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q176"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>353</v>
+      </c>
+      <c r="B177" t="b">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>18</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="s">
+        <v>27</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>58</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177"/>
+      <c r="P177" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q177"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>354</v>
+      </c>
+      <c r="B178" t="b">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>27</v>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="s">
+        <v>58</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="s">
+        <v>28</v>
+      </c>
+      <c r="N178" t="s">
+        <v>29</v>
+      </c>
+      <c r="O178"/>
+      <c r="P178" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q178"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>358</v>
+      </c>
+      <c r="B179" t="b">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>30</v>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="s">
+        <v>56</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="s">
+        <v>57</v>
+      </c>
+      <c r="N179" t="s">
+        <v>32</v>
+      </c>
+      <c r="O179" t="n">
+        <v>7</v>
+      </c>
+      <c r="P179" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>359</v>
+      </c>
+      <c r="B180" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>18</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>30</v>
+      </c>
+      <c r="I180" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="s">
+        <v>56</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="s">
+        <v>57</v>
+      </c>
+      <c r="N180" t="s">
+        <v>32</v>
+      </c>
+      <c r="O180" t="n">
+        <v>7</v>
+      </c>
+      <c r="P180" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>360</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>18</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>30</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="s">
+        <v>56</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="s">
+        <v>57</v>
+      </c>
+      <c r="N181" t="s">
+        <v>32</v>
+      </c>
+      <c r="O181" t="n">
+        <v>7</v>
+      </c>
+      <c r="P181" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>364</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>33</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="s">
+        <v>58</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
+        <v>55</v>
+      </c>
+      <c r="N182" t="s">
+        <v>22</v>
+      </c>
+      <c r="O182" t="n">
+        <v>11</v>
+      </c>
+      <c r="P182" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>365</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>33</v>
+      </c>
+      <c r="I183" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="s">
+        <v>58</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>55</v>
+      </c>
+      <c r="N183" t="s">
+        <v>22</v>
+      </c>
+      <c r="O183" t="n">
+        <v>11</v>
+      </c>
+      <c r="P183" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>366</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>33</v>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="s">
+        <v>58</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>55</v>
+      </c>
+      <c r="N184" t="s">
+        <v>22</v>
+      </c>
+      <c r="O184" t="n">
+        <v>11</v>
+      </c>
+      <c r="P184" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>370</v>
+      </c>
+      <c r="B185" t="b">
+        <v>1</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>34</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="s">
+        <v>56</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="s">
+        <v>25</v>
+      </c>
+      <c r="N185" t="s">
+        <v>26</v>
+      </c>
+      <c r="O185"/>
+      <c r="P185" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q185"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>371</v>
+      </c>
+      <c r="B186" t="b">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="s">
+        <v>34</v>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>56</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="s">
+        <v>25</v>
+      </c>
+      <c r="N186" t="s">
+        <v>26</v>
+      </c>
+      <c r="O186"/>
+      <c r="P186" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>372</v>
+      </c>
+      <c r="B187" t="b">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="s">
+        <v>34</v>
+      </c>
+      <c r="I187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>56</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="s">
+        <v>25</v>
+      </c>
+      <c r="N187" t="s">
+        <v>26</v>
+      </c>
+      <c r="O187"/>
+      <c r="P187" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>376</v>
+      </c>
+      <c r="B188" t="b">
+        <v>1</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="s">
+        <v>35</v>
+      </c>
+      <c r="I188" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="s">
+        <v>58</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188" t="s">
+        <v>29</v>
+      </c>
+      <c r="O188"/>
+      <c r="P188" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q188"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>377</v>
+      </c>
+      <c r="B189" t="b">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="s">
+        <v>35</v>
+      </c>
+      <c r="I189" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="s">
+        <v>58</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
+        <v>29</v>
+      </c>
+      <c r="O189"/>
+      <c r="P189" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q189"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>378</v>
+      </c>
+      <c r="B190" t="b">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="s">
+        <v>35</v>
+      </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="s">
+        <v>58</v>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="s">
+        <v>28</v>
+      </c>
+      <c r="N190" t="s">
+        <v>29</v>
+      </c>
+      <c r="O190"/>
+      <c r="P190" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q190"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>382</v>
+      </c>
+      <c r="B191" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="s">
+        <v>36</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="s">
+        <v>56</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="s">
+        <v>57</v>
+      </c>
+      <c r="N191" t="s">
+        <v>32</v>
+      </c>
+      <c r="O191" t="n">
+        <v>7</v>
+      </c>
+      <c r="P191" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>383</v>
+      </c>
+      <c r="B192" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="s">
+        <v>36</v>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="s">
+        <v>56</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="s">
+        <v>57</v>
+      </c>
+      <c r="N192" t="s">
+        <v>32</v>
+      </c>
+      <c r="O192" t="n">
+        <v>7</v>
+      </c>
+      <c r="P192" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>384</v>
+      </c>
+      <c r="B193" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="s">
+        <v>36</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>56</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>57</v>
+      </c>
+      <c r="N193" t="s">
+        <v>32</v>
+      </c>
+      <c r="O193" t="n">
+        <v>7</v>
+      </c>
+      <c r="P193" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>388</v>
+      </c>
+      <c r="B194" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" t="n">
+        <v>9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>59</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>60</v>
+      </c>
+      <c r="N194" t="s">
+        <v>22</v>
+      </c>
+      <c r="O194" t="n">
+        <v>8</v>
+      </c>
+      <c r="P194" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>389</v>
+      </c>
+      <c r="B195" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>59</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="s">
+        <v>60</v>
+      </c>
+      <c r="N195" t="s">
+        <v>22</v>
+      </c>
+      <c r="O195" t="n">
+        <v>8</v>
+      </c>
+      <c r="P195" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>390</v>
+      </c>
+      <c r="B196" t="b">
+        <v>0</v>
+      </c>
+      <c r="C196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="s">
+        <v>59</v>
+      </c>
+      <c r="L196" t="n">
+        <v>3</v>
+      </c>
+      <c r="M196" t="s">
+        <v>60</v>
+      </c>
+      <c r="N196" t="s">
+        <v>22</v>
+      </c>
+      <c r="O196" t="n">
+        <v>8</v>
+      </c>
+      <c r="P196" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>394</v>
+      </c>
+      <c r="B197" t="b">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="s">
+        <v>56</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="s">
+        <v>25</v>
+      </c>
+      <c r="N197" t="s">
+        <v>26</v>
+      </c>
+      <c r="O197"/>
+      <c r="P197" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q197"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>395</v>
+      </c>
+      <c r="B198" t="b">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="s">
+        <v>56</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="s">
+        <v>25</v>
+      </c>
+      <c r="N198" t="s">
+        <v>26</v>
+      </c>
+      <c r="O198"/>
+      <c r="P198" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q198"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>396</v>
+      </c>
+      <c r="B199" t="b">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="s">
+        <v>56</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="s">
+        <v>25</v>
+      </c>
+      <c r="N199" t="s">
+        <v>26</v>
+      </c>
+      <c r="O199"/>
+      <c r="P199" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q199"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>400</v>
+      </c>
+      <c r="B200" t="b">
+        <v>1</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="s">
+        <v>27</v>
+      </c>
+      <c r="I200" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="s">
+        <v>59</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="s">
+        <v>28</v>
+      </c>
+      <c r="N200" t="s">
+        <v>29</v>
+      </c>
+      <c r="O200"/>
+      <c r="P200" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q200"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>401</v>
+      </c>
+      <c r="B201" t="b">
+        <v>1</v>
+      </c>
+      <c r="C201" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>59</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>28</v>
+      </c>
+      <c r="N201" t="s">
+        <v>29</v>
+      </c>
+      <c r="O201"/>
+      <c r="P201" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q201"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>402</v>
+      </c>
+      <c r="B202" t="b">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="s">
+        <v>27</v>
+      </c>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>59</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="s">
+        <v>28</v>
+      </c>
+      <c r="N202" t="s">
+        <v>29</v>
+      </c>
+      <c r="O202"/>
+      <c r="P202" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q202"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>406</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="s">
+        <v>30</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>56</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>57</v>
+      </c>
+      <c r="N203" t="s">
+        <v>32</v>
+      </c>
+      <c r="O203" t="n">
+        <v>7</v>
+      </c>
+      <c r="P203" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>407</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="s">
+        <v>30</v>
+      </c>
+      <c r="I204" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>56</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="s">
+        <v>57</v>
+      </c>
+      <c r="N204" t="s">
+        <v>32</v>
+      </c>
+      <c r="O204" t="n">
+        <v>7</v>
+      </c>
+      <c r="P204" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>408</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="s">
+        <v>30</v>
+      </c>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="s">
+        <v>56</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="s">
+        <v>57</v>
+      </c>
+      <c r="N205" t="s">
+        <v>32</v>
+      </c>
+      <c r="O205" t="n">
+        <v>7</v>
+      </c>
+      <c r="P205" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>412</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="s">
+        <v>33</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>59</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>60</v>
+      </c>
+      <c r="N206" t="s">
+        <v>22</v>
+      </c>
+      <c r="O206" t="n">
+        <v>8</v>
+      </c>
+      <c r="P206" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>413</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="s">
+        <v>33</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>59</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="s">
+        <v>60</v>
+      </c>
+      <c r="N207" t="s">
+        <v>22</v>
+      </c>
+      <c r="O207" t="n">
+        <v>8</v>
+      </c>
+      <c r="P207" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>414</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="s">
+        <v>33</v>
+      </c>
+      <c r="I208" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>59</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>60</v>
+      </c>
+      <c r="N208" t="s">
+        <v>22</v>
+      </c>
+      <c r="O208" t="n">
+        <v>8</v>
+      </c>
+      <c r="P208" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>418</v>
+      </c>
+      <c r="B209" t="b">
+        <v>1</v>
+      </c>
+      <c r="C209" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="s">
+        <v>34</v>
+      </c>
+      <c r="I209" t="n">
+        <v>9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>56</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>25</v>
+      </c>
+      <c r="N209" t="s">
+        <v>26</v>
+      </c>
+      <c r="O209"/>
+      <c r="P209" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q209"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>419</v>
+      </c>
+      <c r="B210" t="b">
+        <v>1</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>18</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="s">
+        <v>34</v>
+      </c>
+      <c r="I210" t="n">
+        <v>9</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="s">
+        <v>56</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="s">
+        <v>25</v>
+      </c>
+      <c r="N210" t="s">
+        <v>26</v>
+      </c>
+      <c r="O210"/>
+      <c r="P210" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>420</v>
+      </c>
+      <c r="B211" t="b">
+        <v>1</v>
+      </c>
+      <c r="C211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="s">
+        <v>34</v>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="s">
+        <v>56</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>25</v>
+      </c>
+      <c r="N211" t="s">
+        <v>26</v>
+      </c>
+      <c r="O211"/>
+      <c r="P211" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q211"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>424</v>
+      </c>
+      <c r="B212" t="b">
+        <v>1</v>
+      </c>
+      <c r="C212" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="s">
+        <v>35</v>
+      </c>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="s">
+        <v>59</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="s">
+        <v>28</v>
+      </c>
+      <c r="N212" t="s">
+        <v>29</v>
+      </c>
+      <c r="O212"/>
+      <c r="P212" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>425</v>
+      </c>
+      <c r="B213" t="b">
+        <v>1</v>
+      </c>
+      <c r="C213" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213" t="s">
+        <v>18</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="s">
+        <v>35</v>
+      </c>
+      <c r="I213" t="n">
+        <v>9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>59</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="s">
+        <v>28</v>
+      </c>
+      <c r="N213" t="s">
+        <v>29</v>
+      </c>
+      <c r="O213"/>
+      <c r="P213" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q213"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>426</v>
+      </c>
+      <c r="B214" t="b">
+        <v>1</v>
+      </c>
+      <c r="C214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="s">
+        <v>35</v>
+      </c>
+      <c r="I214" t="n">
+        <v>9</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>59</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="s">
+        <v>28</v>
+      </c>
+      <c r="N214" t="s">
+        <v>29</v>
+      </c>
+      <c r="O214"/>
+      <c r="P214" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>430</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="s">
+        <v>36</v>
+      </c>
+      <c r="I215" t="n">
+        <v>9</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>56</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="s">
+        <v>57</v>
+      </c>
+      <c r="N215" t="s">
+        <v>32</v>
+      </c>
+      <c r="O215" t="n">
+        <v>7</v>
+      </c>
+      <c r="P215" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>431</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" t="s">
+        <v>18</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="s">
+        <v>36</v>
+      </c>
+      <c r="I216" t="n">
+        <v>9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="s">
+        <v>56</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="s">
+        <v>57</v>
+      </c>
+      <c r="N216" t="s">
+        <v>32</v>
+      </c>
+      <c r="O216" t="n">
+        <v>7</v>
+      </c>
+      <c r="P216" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>432</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="s">
+        <v>36</v>
+      </c>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="s">
+        <v>56</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="s">
+        <v>57</v>
+      </c>
+      <c r="N217" t="s">
+        <v>32</v>
+      </c>
+      <c r="O217" t="n">
+        <v>7</v>
+      </c>
+      <c r="P217" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e5", "e6", "e9", "e38", "e366", "e376", "e389", "e394", "e406", "e430", "e461", "e484", "e497", "e510", "e512", "e513")</t>
+    <t xml:space="preserve">c("e5", "e6", "e38", "e366", "e376", "e389", "e394", "e406", "e430", "e461", "e497", "e510", "e512")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e10", "e55", "e67", "e382", "e384", "e395", "e422", "e455", "e473", "e496")</t>
+    <t xml:space="preserve">c("e10", "e55", "e382", "e384", "e395", "e422", "e455", "e473", "e496")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">c("e52", "e53", "e54", "e66", "e430", "e497")</t>
@@ -107,11 +107,11 @@
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
-2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 141, 142, 143, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
+2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e4", "e18", "e33", "e36", "e47", "e55", "e56", "e57", "e60", "e61", "e67", "e68", "e69", "e381", "e391", "e392", "e410", "e415", "e420", "e421", "e423", "e439", "e448", "e455", "e470", "e473", "e474", "e488", "e496", "e504", "e515", "e517")</t>
+    <t xml:space="preserve">c("e4", "e33", "e36", "e47", "e55", "e56", "e57", "e60", "e61", "e68", "e69", "e381", "e391", "e410", "e415", "e420", "e421", "e423", "e448", "e455", "e470", "e473", "e474", "e488", "e496", "e515", "e517")</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
@@ -126,12 +126,6 @@
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
@@ -141,54 +135,49 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
-2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
-2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
+    <t xml:space="preserve">c(177, 180, 229, 230, 231, 233, 234, 235, 236)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
@@ -197,7 +186,7 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2289, 2290)</t>
   </si>
 </sst>
 </file>
@@ -623,13 +612,13 @@
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -676,13 +665,13 @@
         <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -729,13 +718,13 @@
         <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5">
@@ -782,13 +771,13 @@
         <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q5" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6">
@@ -835,13 +824,13 @@
         <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -888,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q7" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
@@ -944,10 +933,10 @@
         <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
@@ -997,10 +986,10 @@
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -1050,10 +1039,10 @@
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -1100,13 +1089,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P11" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="12">
@@ -1153,13 +1142,13 @@
         <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P12" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q12" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="13">
@@ -1206,13 +1195,13 @@
         <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q13" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1248,13 @@
         <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q14" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
@@ -1312,13 +1301,13 @@
         <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P15" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16">
@@ -1365,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q16" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17">
@@ -1418,13 +1407,13 @@
         <v>26</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
@@ -1471,13 +1460,13 @@
         <v>26</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P18" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q18" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19">
@@ -1524,13 +1513,13 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q19" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20">
@@ -1580,10 +1569,10 @@
         <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q20" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21">
@@ -1633,10 +1622,10 @@
         <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q21" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22">
@@ -1686,10 +1675,10 @@
         <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q22" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23">
@@ -1736,13 +1725,13 @@
         <v>32</v>
       </c>
       <c r="O23" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P23" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q23" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="24">
@@ -1789,13 +1778,13 @@
         <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P24" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="25">
@@ -1842,13 +1831,13 @@
         <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P25" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q25" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="26">
@@ -1883,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1895,13 +1884,13 @@
         <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P26" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q26" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27">
@@ -1936,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -1948,13 +1937,13 @@
         <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P27" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q27" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
@@ -1989,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2001,13 +1990,13 @@
         <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P28" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q28" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29">
@@ -2042,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2054,13 +2043,13 @@
         <v>26</v>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P29" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q29" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
@@ -2095,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2107,13 +2096,13 @@
         <v>26</v>
       </c>
       <c r="O30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q30" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31">
@@ -2148,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -2160,13 +2149,13 @@
         <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P31" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q31" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32">
@@ -2201,7 +2190,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2216,10 +2205,10 @@
         <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q32" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33">
@@ -2254,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2269,10 +2258,10 @@
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q33" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34">
@@ -2307,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2322,10 +2311,10 @@
         <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q34" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35">
@@ -2360,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2372,13 +2361,13 @@
         <v>32</v>
       </c>
       <c r="O35" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P35" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q35" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="36">
@@ -2413,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2425,13 +2414,13 @@
         <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P36" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q36" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="37">
@@ -2466,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -2478,13 +2467,13 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P37" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q37" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="38">
@@ -2519,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2531,13 +2520,13 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P38" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q38" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39">
@@ -2572,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2584,13 +2573,13 @@
         <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P39" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q39" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40">
@@ -2625,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2637,13 +2626,13 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q40" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="41">
@@ -2678,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2690,13 +2679,13 @@
         <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P41" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q41" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42">
@@ -2731,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2743,13 +2732,13 @@
         <v>26</v>
       </c>
       <c r="O42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P42" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q42" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43">
@@ -2784,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -2796,13 +2785,13 @@
         <v>26</v>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P43" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q43" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44">
@@ -2837,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2852,10 +2841,10 @@
         <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q44" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45">
@@ -2890,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -2905,10 +2894,10 @@
         <v>6</v>
       </c>
       <c r="P45" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q45" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46">
@@ -2943,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -2958,10 +2947,10 @@
         <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q46" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47">
@@ -2996,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -3008,13 +2997,13 @@
         <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P47" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q47" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="48">
@@ -3049,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3061,13 +3050,13 @@
         <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P48" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q48" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="49">
@@ -3102,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -3114,13 +3103,13 @@
         <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P49" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q49" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="50">
@@ -3155,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3167,13 +3156,13 @@
         <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P50" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q50" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51">
@@ -3208,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3220,13 +3209,13 @@
         <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P51" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q51" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52">
@@ -3261,7 +3250,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3273,13 +3262,13 @@
         <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P52" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q52" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53">
@@ -3314,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3326,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P53" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q53" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54">
@@ -3367,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3379,13 +3368,13 @@
         <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q54" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55">
@@ -3420,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3432,13 +3421,13 @@
         <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P55" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q55" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56">
@@ -3473,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3488,10 +3477,10 @@
         <v>6</v>
       </c>
       <c r="P56" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q56" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
@@ -3526,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3541,10 +3530,10 @@
         <v>6</v>
       </c>
       <c r="P57" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q57" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58">
@@ -3579,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3594,10 +3583,10 @@
         <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q58" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59">
@@ -3632,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3644,13 +3633,13 @@
         <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P59" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q59" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="60">
@@ -3685,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3697,13 +3686,13 @@
         <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P60" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q60" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="61">
@@ -3738,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3750,13 +3739,13 @@
         <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P61" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q61" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="62">
@@ -3791,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3803,13 +3792,13 @@
         <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P62" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q62" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63">
@@ -3844,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3856,13 +3845,13 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P63" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q63" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64">
@@ -3897,7 +3886,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3909,13 +3898,13 @@
         <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P64" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q64" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65">
@@ -3950,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3962,13 +3951,13 @@
         <v>26</v>
       </c>
       <c r="O65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P65" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q65" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66">
@@ -4003,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -4015,13 +4004,13 @@
         <v>26</v>
       </c>
       <c r="O66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P66" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q66" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67">
@@ -4056,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4068,13 +4057,13 @@
         <v>26</v>
       </c>
       <c r="O67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P67" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q67" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68">
@@ -4109,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4124,10 +4113,10 @@
         <v>6</v>
       </c>
       <c r="P68" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q68" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69">
@@ -4162,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4177,10 +4166,10 @@
         <v>6</v>
       </c>
       <c r="P69" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q69" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70">
@@ -4215,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4230,10 +4219,10 @@
         <v>6</v>
       </c>
       <c r="P70" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q70" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71">
@@ -4268,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4280,13 +4269,13 @@
         <v>32</v>
       </c>
       <c r="O71" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P71" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q71" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="72">
@@ -4321,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4333,13 +4322,13 @@
         <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P72" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q72" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="73">
@@ -4374,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4386,13 +4375,13 @@
         <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P73" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q73" t="n">
-        <v>811</v>
+        <v>712</v>
       </c>
     </row>
     <row r="74">
@@ -4427,7 +4416,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4439,13 +4428,13 @@
         <v>22</v>
       </c>
       <c r="O74" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P74" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q74" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75">
@@ -4480,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4492,13 +4481,13 @@
         <v>22</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P75" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q75" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76">
@@ -4533,7 +4522,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4545,13 +4534,13 @@
         <v>22</v>
       </c>
       <c r="O76" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P76" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q76" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
@@ -4586,13 +4575,13 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
@@ -4601,10 +4590,10 @@
         <v>7</v>
       </c>
       <c r="P77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q77" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78">
@@ -4639,13 +4628,13 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
@@ -4654,10 +4643,10 @@
         <v>7</v>
       </c>
       <c r="P78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q78" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79">
@@ -4692,13 +4681,13 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
@@ -4707,10 +4696,10 @@
         <v>7</v>
       </c>
       <c r="P79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q79" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
@@ -4745,7 +4734,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4760,10 +4749,10 @@
         <v>6</v>
       </c>
       <c r="P80" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q80" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81">
@@ -4798,7 +4787,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4813,10 +4802,10 @@
         <v>6</v>
       </c>
       <c r="P81" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q81" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="82">
@@ -4851,7 +4840,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4866,10 +4855,10 @@
         <v>6</v>
       </c>
       <c r="P82" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q82" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83">
@@ -4904,25 +4893,25 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
+        <v>40</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="s">
         <v>42</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="s">
-        <v>44</v>
       </c>
       <c r="N83" t="s">
         <v>32</v>
       </c>
       <c r="O83" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P83" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q83" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
     </row>
     <row r="84">
@@ -4957,25 +4946,25 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
+        <v>40</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="s">
         <v>42</v>
-      </c>
-      <c r="L84" t="n">
-        <v>2</v>
-      </c>
-      <c r="M84" t="s">
-        <v>44</v>
       </c>
       <c r="N84" t="s">
         <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P84" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q84" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
     </row>
     <row r="85">
@@ -5010,25 +4999,25 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
+        <v>40</v>
+      </c>
+      <c r="L85" t="n">
+        <v>3</v>
+      </c>
+      <c r="M85" t="s">
         <v>42</v>
-      </c>
-      <c r="L85" t="n">
-        <v>3</v>
-      </c>
-      <c r="M85" t="s">
-        <v>44</v>
       </c>
       <c r="N85" t="s">
         <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P85" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q85" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
     </row>
     <row r="86">
@@ -5063,7 +5052,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5075,13 +5064,13 @@
         <v>22</v>
       </c>
       <c r="O86" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P86" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q86" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87">
@@ -5116,7 +5105,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5128,13 +5117,13 @@
         <v>22</v>
       </c>
       <c r="O87" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P87" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q87" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="88">
@@ -5169,7 +5158,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5181,13 +5170,13 @@
         <v>22</v>
       </c>
       <c r="O88" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P88" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q88" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="89">
@@ -5222,13 +5211,13 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
@@ -5237,10 +5226,10 @@
         <v>7</v>
       </c>
       <c r="P89" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q89" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90">
@@ -5275,13 +5264,13 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
@@ -5290,10 +5279,10 @@
         <v>7</v>
       </c>
       <c r="P90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q90" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91">
@@ -5328,13 +5317,13 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
@@ -5343,10 +5332,10 @@
         <v>7</v>
       </c>
       <c r="P91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q91" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92">
@@ -5381,7 +5370,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5396,10 +5385,10 @@
         <v>6</v>
       </c>
       <c r="P92" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q92" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="93">
@@ -5434,7 +5423,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5449,10 +5438,10 @@
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q93" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94">
@@ -5487,7 +5476,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5502,10 +5491,10 @@
         <v>6</v>
       </c>
       <c r="P94" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q94" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="95">
@@ -5540,25 +5529,25 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
+        <v>40</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="s">
         <v>42</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="s">
-        <v>44</v>
       </c>
       <c r="N95" t="s">
         <v>32</v>
       </c>
       <c r="O95" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P95" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q95" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
     </row>
     <row r="96">
@@ -5593,25 +5582,25 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
+        <v>40</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" t="s">
         <v>42</v>
-      </c>
-      <c r="L96" t="n">
-        <v>2</v>
-      </c>
-      <c r="M96" t="s">
-        <v>44</v>
       </c>
       <c r="N96" t="s">
         <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P96" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q96" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
     </row>
     <row r="97">
@@ -5646,25 +5635,25 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
+        <v>40</v>
+      </c>
+      <c r="L97" t="n">
+        <v>3</v>
+      </c>
+      <c r="M97" t="s">
         <v>42</v>
-      </c>
-      <c r="L97" t="n">
-        <v>3</v>
-      </c>
-      <c r="M97" t="s">
-        <v>44</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
       </c>
       <c r="O97" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P97" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="Q97" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
     </row>
     <row r="98">
@@ -5699,7 +5688,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -5711,13 +5700,13 @@
         <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P98" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q98" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99">
@@ -5752,7 +5741,7 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
@@ -5764,13 +5753,13 @@
         <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P99" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q99" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100">
@@ -5805,7 +5794,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
@@ -5817,13 +5806,13 @@
         <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P100" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q100" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101">
@@ -5858,25 +5847,25 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N101" t="s">
         <v>26</v>
       </c>
       <c r="O101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P101" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q101" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102">
@@ -5911,25 +5900,25 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N102" t="s">
         <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P102" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q102" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103">
@@ -5964,25 +5953,25 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N103" t="s">
         <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P103" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q103" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104">
@@ -6017,7 +6006,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6032,10 +6021,10 @@
         <v>6</v>
       </c>
       <c r="P104" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q104" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="105">
@@ -6070,7 +6059,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6085,10 +6074,10 @@
         <v>6</v>
       </c>
       <c r="P105" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q105" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="106">
@@ -6123,7 +6112,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6138,10 +6127,10 @@
         <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q106" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107">
@@ -6176,25 +6165,25 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
+        <v>44</v>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="s">
         <v>46</v>
-      </c>
-      <c r="L107" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" t="s">
-        <v>48</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
       </c>
       <c r="O107" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P107" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q107" t="n">
-        <v>728</v>
+        <v>629</v>
       </c>
     </row>
     <row r="108">
@@ -6229,25 +6218,25 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
+        <v>44</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" t="s">
         <v>46</v>
-      </c>
-      <c r="L108" t="n">
-        <v>2</v>
-      </c>
-      <c r="M108" t="s">
-        <v>48</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P108" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q108" t="n">
-        <v>728</v>
+        <v>629</v>
       </c>
     </row>
     <row r="109">
@@ -6282,25 +6271,25 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
+        <v>44</v>
+      </c>
+      <c r="L109" t="n">
+        <v>3</v>
+      </c>
+      <c r="M109" t="s">
         <v>46</v>
-      </c>
-      <c r="L109" t="n">
-        <v>3</v>
-      </c>
-      <c r="M109" t="s">
-        <v>48</v>
       </c>
       <c r="N109" t="s">
         <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P109" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q109" t="n">
-        <v>728</v>
+        <v>629</v>
       </c>
     </row>
     <row r="110">
@@ -6335,7 +6324,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -6347,13 +6336,13 @@
         <v>22</v>
       </c>
       <c r="O110" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P110" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q110" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="111">
@@ -6388,7 +6377,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
@@ -6400,13 +6389,13 @@
         <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P111" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q111" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="112">
@@ -6441,7 +6430,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
@@ -6453,13 +6442,13 @@
         <v>22</v>
       </c>
       <c r="O112" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P112" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Q112" t="n">
-        <v>395</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113">
@@ -6494,25 +6483,25 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N113" t="s">
         <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P113" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q113" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114">
@@ -6547,25 +6536,25 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N114" t="s">
         <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P114" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q114" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115">
@@ -6600,25 +6589,25 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N115" t="s">
         <v>26</v>
       </c>
       <c r="O115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P115" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q115" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="116">
@@ -6653,7 +6642,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6668,10 +6657,10 @@
         <v>6</v>
       </c>
       <c r="P116" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q116" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117">
@@ -6706,7 +6695,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6721,10 +6710,10 @@
         <v>6</v>
       </c>
       <c r="P117" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q117" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118">
@@ -6759,7 +6748,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6774,10 +6763,10 @@
         <v>6</v>
       </c>
       <c r="P118" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q118" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="119">
@@ -6812,25 +6801,25 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
+        <v>44</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="s">
         <v>46</v>
-      </c>
-      <c r="L119" t="n">
-        <v>1</v>
-      </c>
-      <c r="M119" t="s">
-        <v>48</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
       </c>
       <c r="O119" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P119" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q119" t="n">
-        <v>728</v>
+        <v>629</v>
       </c>
     </row>
     <row r="120">
@@ -6865,25 +6854,25 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
+        <v>44</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2</v>
+      </c>
+      <c r="M120" t="s">
         <v>46</v>
-      </c>
-      <c r="L120" t="n">
-        <v>2</v>
-      </c>
-      <c r="M120" t="s">
-        <v>48</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
       </c>
       <c r="O120" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P120" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q120" t="n">
-        <v>728</v>
+        <v>629</v>
       </c>
     </row>
     <row r="121">
@@ -6918,25 +6907,25 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
+        <v>44</v>
+      </c>
+      <c r="L121" t="n">
+        <v>3</v>
+      </c>
+      <c r="M121" t="s">
         <v>46</v>
-      </c>
-      <c r="L121" t="n">
-        <v>3</v>
-      </c>
-      <c r="M121" t="s">
-        <v>48</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
       </c>
       <c r="O121" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P121" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="Q121" t="n">
-        <v>728</v>
+        <v>629</v>
       </c>
     </row>
     <row r="122">
@@ -6971,25 +6960,25 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P122" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q122" t="n">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123">
@@ -7024,25 +7013,25 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P123" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q123" t="n">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="124">
@@ -7077,25 +7066,25 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P124" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q124" t="n">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="125">
@@ -7130,25 +7119,25 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N125" t="s">
         <v>26</v>
       </c>
       <c r="O125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P125" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q125" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="126">
@@ -7183,25 +7172,25 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N126" t="s">
         <v>26</v>
       </c>
       <c r="O126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P126" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q126" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="127">
@@ -7236,25 +7225,25 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N127" t="s">
         <v>26</v>
       </c>
       <c r="O127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P127" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q127" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="128">
@@ -7262,7 +7251,7 @@
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
@@ -7289,33 +7278,29 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
       </c>
-      <c r="O128" t="n">
-        <v>3</v>
-      </c>
+      <c r="O128"/>
       <c r="P128" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>62</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q128"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -7342,33 +7327,29 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
       </c>
-      <c r="O129" t="n">
-        <v>3</v>
-      </c>
+      <c r="O129"/>
       <c r="P129" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>62</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q129"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -7395,26 +7376,22 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
       </c>
-      <c r="O130" t="n">
-        <v>3</v>
-      </c>
+      <c r="O130"/>
       <c r="P130" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>62</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q130"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7448,25 +7425,25 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N131" t="s">
         <v>32</v>
       </c>
       <c r="O131" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P131" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q131" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
     </row>
     <row r="132">
@@ -7501,25 +7478,25 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N132" t="s">
         <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P132" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q132" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
     </row>
     <row r="133">
@@ -7554,25 +7531,25 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N133" t="s">
         <v>32</v>
       </c>
       <c r="O133" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P133" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q133" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
     </row>
     <row r="134">
@@ -7607,25 +7584,25 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P134" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q134" t="n">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="135">
@@ -7660,25 +7637,25 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P135" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q135" t="n">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="136">
@@ -7713,25 +7690,25 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P136" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q136" t="n">
-        <v>251</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137">
@@ -7766,25 +7743,25 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N137" t="s">
         <v>26</v>
       </c>
       <c r="O137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P137" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q137" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="138">
@@ -7819,25 +7796,25 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N138" t="s">
         <v>26</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P138" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q138" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="139">
@@ -7872,25 +7849,25 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N139" t="s">
         <v>26</v>
       </c>
       <c r="O139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P139" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="Q139" t="n">
-        <v>161</v>
+        <v>133</v>
       </c>
     </row>
     <row r="140">
@@ -7925,26 +7902,22 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
       </c>
-      <c r="O140" t="n">
-        <v>3</v>
-      </c>
+      <c r="O140"/>
       <c r="P140" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>62</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q140"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7978,26 +7951,22 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
       </c>
-      <c r="O141" t="n">
-        <v>3</v>
-      </c>
+      <c r="O141"/>
       <c r="P141" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>62</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q141"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8031,26 +8000,22 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
       </c>
-      <c r="O142" t="n">
-        <v>3</v>
-      </c>
+      <c r="O142"/>
       <c r="P142" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>62</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="Q142"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8084,25 +8049,25 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N143" t="s">
         <v>32</v>
       </c>
       <c r="O143" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P143" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q143" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
     </row>
     <row r="144">
@@ -8137,25 +8102,25 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N144" t="s">
         <v>32</v>
       </c>
       <c r="O144" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P144" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q144" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
     </row>
     <row r="145">
@@ -8190,25 +8155,25 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N145" t="s">
         <v>32</v>
       </c>
       <c r="O145" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P145" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q145" t="n">
-        <v>702</v>
+        <v>607</v>
       </c>
     </row>
     <row r="146">
@@ -8243,25 +8208,25 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N146" t="s">
         <v>22</v>
       </c>
       <c r="O146" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P146" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q146" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="147">
@@ -8296,25 +8261,25 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N147" t="s">
         <v>22</v>
       </c>
       <c r="O147" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P147" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q147" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="148">
@@ -8349,25 +8314,25 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N148" t="s">
         <v>22</v>
       </c>
       <c r="O148" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P148" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q148" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="149">
@@ -8402,7 +8367,7 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
@@ -8415,7 +8380,7 @@
       </c>
       <c r="O149"/>
       <c r="P149" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q149"/>
     </row>
@@ -8451,7 +8416,7 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
@@ -8464,7 +8429,7 @@
       </c>
       <c r="O150"/>
       <c r="P150" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q150"/>
     </row>
@@ -8500,7 +8465,7 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
@@ -8513,7 +8478,7 @@
       </c>
       <c r="O151"/>
       <c r="P151" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q151"/>
     </row>
@@ -8549,7 +8514,7 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
@@ -8562,7 +8527,7 @@
       </c>
       <c r="O152"/>
       <c r="P152" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q152"/>
     </row>
@@ -8598,7 +8563,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
@@ -8611,7 +8576,7 @@
       </c>
       <c r="O153"/>
       <c r="P153" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q153"/>
     </row>
@@ -8647,7 +8612,7 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
@@ -8660,7 +8625,7 @@
       </c>
       <c r="O154"/>
       <c r="P154" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q154"/>
     </row>
@@ -8696,25 +8661,25 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N155" t="s">
         <v>32</v>
       </c>
       <c r="O155" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P155" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q155" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156">
@@ -8749,25 +8714,25 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N156" t="s">
         <v>32</v>
       </c>
       <c r="O156" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q156" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="157">
@@ -8802,25 +8767,25 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N157" t="s">
         <v>32</v>
       </c>
       <c r="O157" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P157" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q157" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="158">
@@ -8855,25 +8820,25 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N158" t="s">
         <v>22</v>
       </c>
       <c r="O158" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P158" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q158" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="159">
@@ -8908,25 +8873,25 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N159" t="s">
         <v>22</v>
       </c>
       <c r="O159" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P159" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q159" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="160">
@@ -8961,25 +8926,25 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N160" t="s">
         <v>22</v>
       </c>
       <c r="O160" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P160" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q160" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="161">
@@ -9014,7 +8979,7 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
@@ -9027,7 +8992,7 @@
       </c>
       <c r="O161"/>
       <c r="P161" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q161"/>
     </row>
@@ -9063,7 +9028,7 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
@@ -9076,7 +9041,7 @@
       </c>
       <c r="O162"/>
       <c r="P162" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q162"/>
     </row>
@@ -9112,7 +9077,7 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -9125,7 +9090,7 @@
       </c>
       <c r="O163"/>
       <c r="P163" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q163"/>
     </row>
@@ -9161,7 +9126,7 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
@@ -9174,7 +9139,7 @@
       </c>
       <c r="O164"/>
       <c r="P164" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q164"/>
     </row>
@@ -9210,7 +9175,7 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
@@ -9223,7 +9188,7 @@
       </c>
       <c r="O165"/>
       <c r="P165" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q165"/>
     </row>
@@ -9259,7 +9224,7 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9272,7 +9237,7 @@
       </c>
       <c r="O166"/>
       <c r="P166" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q166"/>
     </row>
@@ -9308,25 +9273,25 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N167" t="s">
         <v>32</v>
       </c>
       <c r="O167" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P167" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q167" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="168">
@@ -9361,25 +9326,25 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N168" t="s">
         <v>32</v>
       </c>
       <c r="O168" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P168" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q168" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="169">
@@ -9414,25 +9379,25 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N169" t="s">
         <v>32</v>
       </c>
       <c r="O169" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P169" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q169" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="170">
@@ -9467,25 +9432,25 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N170" t="s">
         <v>22</v>
       </c>
       <c r="O170" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P170" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q170" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="171">
@@ -9520,25 +9485,25 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N171" t="s">
         <v>22</v>
       </c>
       <c r="O171" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P171" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q171" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="172">
@@ -9573,25 +9538,25 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N172" t="s">
         <v>22</v>
       </c>
       <c r="O172" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P172" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q172" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="173">
@@ -9626,7 +9591,7 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
@@ -9639,7 +9604,7 @@
       </c>
       <c r="O173"/>
       <c r="P173" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q173"/>
     </row>
@@ -9675,7 +9640,7 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
@@ -9688,7 +9653,7 @@
       </c>
       <c r="O174"/>
       <c r="P174" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q174"/>
     </row>
@@ -9724,7 +9689,7 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
@@ -9737,7 +9702,7 @@
       </c>
       <c r="O175"/>
       <c r="P175" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q175"/>
     </row>
@@ -9773,7 +9738,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -9786,7 +9751,7 @@
       </c>
       <c r="O176"/>
       <c r="P176" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q176"/>
     </row>
@@ -9822,7 +9787,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
@@ -9835,7 +9800,7 @@
       </c>
       <c r="O177"/>
       <c r="P177" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q177"/>
     </row>
@@ -9871,7 +9836,7 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
@@ -9884,7 +9849,7 @@
       </c>
       <c r="O178"/>
       <c r="P178" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q178"/>
     </row>
@@ -9920,25 +9885,25 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N179" t="s">
         <v>32</v>
       </c>
       <c r="O179" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P179" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q179" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="180">
@@ -9973,25 +9938,25 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N180" t="s">
         <v>32</v>
       </c>
       <c r="O180" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P180" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q180" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="181">
@@ -10026,25 +9991,25 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N181" t="s">
         <v>32</v>
       </c>
       <c r="O181" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P181" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q181" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="182">
@@ -10079,25 +10044,25 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N182" t="s">
         <v>22</v>
       </c>
       <c r="O182" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P182" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q182" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="183">
@@ -10132,25 +10097,25 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N183" t="s">
         <v>22</v>
       </c>
       <c r="O183" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P183" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q183" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="184">
@@ -10185,25 +10150,25 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N184" t="s">
         <v>22</v>
       </c>
       <c r="O184" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P184" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q184" t="n">
-        <v>298</v>
+        <v>155</v>
       </c>
     </row>
     <row r="185">
@@ -10238,7 +10203,7 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
@@ -10251,7 +10216,7 @@
       </c>
       <c r="O185"/>
       <c r="P185" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q185"/>
     </row>
@@ -10287,7 +10252,7 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
@@ -10300,7 +10265,7 @@
       </c>
       <c r="O186"/>
       <c r="P186" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q186"/>
     </row>
@@ -10336,7 +10301,7 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
@@ -10349,7 +10314,7 @@
       </c>
       <c r="O187"/>
       <c r="P187" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q187"/>
     </row>
@@ -10385,7 +10350,7 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
@@ -10398,7 +10363,7 @@
       </c>
       <c r="O188"/>
       <c r="P188" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q188"/>
     </row>
@@ -10434,7 +10399,7 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
@@ -10447,7 +10412,7 @@
       </c>
       <c r="O189"/>
       <c r="P189" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q189"/>
     </row>
@@ -10483,7 +10448,7 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
@@ -10496,7 +10461,7 @@
       </c>
       <c r="O190"/>
       <c r="P190" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q190"/>
     </row>
@@ -10532,25 +10497,25 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N191" t="s">
         <v>32</v>
       </c>
       <c r="O191" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P191" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q191" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="192">
@@ -10585,25 +10550,25 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N192" t="s">
         <v>32</v>
       </c>
       <c r="O192" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P192" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q192" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="193">
@@ -10638,25 +10603,25 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N193" t="s">
         <v>32</v>
       </c>
       <c r="O193" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P193" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q193" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="194">
@@ -10691,25 +10656,25 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N194" t="s">
         <v>22</v>
       </c>
       <c r="O194" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P194" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q194" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="195">
@@ -10744,25 +10709,25 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N195" t="s">
         <v>22</v>
       </c>
       <c r="O195" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P195" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q195" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="196">
@@ -10797,25 +10762,25 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N196" t="s">
         <v>22</v>
       </c>
       <c r="O196" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P196" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q196" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="197">
@@ -10850,7 +10815,7 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
@@ -10863,7 +10828,7 @@
       </c>
       <c r="O197"/>
       <c r="P197" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q197"/>
     </row>
@@ -10899,7 +10864,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
@@ -10912,7 +10877,7 @@
       </c>
       <c r="O198"/>
       <c r="P198" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q198"/>
     </row>
@@ -10948,7 +10913,7 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
@@ -10961,7 +10926,7 @@
       </c>
       <c r="O199"/>
       <c r="P199" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q199"/>
     </row>
@@ -10997,7 +10962,7 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
@@ -11010,7 +10975,7 @@
       </c>
       <c r="O200"/>
       <c r="P200" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q200"/>
     </row>
@@ -11046,7 +11011,7 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
@@ -11059,7 +11024,7 @@
       </c>
       <c r="O201"/>
       <c r="P201" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q201"/>
     </row>
@@ -11095,7 +11060,7 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
@@ -11108,7 +11073,7 @@
       </c>
       <c r="O202"/>
       <c r="P202" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q202"/>
     </row>
@@ -11144,25 +11109,25 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N203" t="s">
         <v>32</v>
       </c>
       <c r="O203" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P203" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q203" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204">
@@ -11197,25 +11162,25 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N204" t="s">
         <v>32</v>
       </c>
       <c r="O204" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P204" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q204" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205">
@@ -11250,25 +11215,25 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N205" t="s">
         <v>32</v>
       </c>
       <c r="O205" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P205" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q205" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206">
@@ -11303,25 +11268,25 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N206" t="s">
         <v>22</v>
       </c>
       <c r="O206" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P206" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q206" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="207">
@@ -11356,25 +11321,25 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N207" t="s">
         <v>22</v>
       </c>
       <c r="O207" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P207" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q207" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="208">
@@ -11409,25 +11374,25 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N208" t="s">
         <v>22</v>
       </c>
       <c r="O208" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P208" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q208" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="209">
@@ -11462,7 +11427,7 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
@@ -11475,7 +11440,7 @@
       </c>
       <c r="O209"/>
       <c r="P209" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q209"/>
     </row>
@@ -11511,7 +11476,7 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
@@ -11524,7 +11489,7 @@
       </c>
       <c r="O210"/>
       <c r="P210" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q210"/>
     </row>
@@ -11560,7 +11525,7 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
@@ -11573,7 +11538,7 @@
       </c>
       <c r="O211"/>
       <c r="P211" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q211"/>
     </row>
@@ -11609,7 +11574,7 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
@@ -11622,7 +11587,7 @@
       </c>
       <c r="O212"/>
       <c r="P212" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q212"/>
     </row>
@@ -11658,7 +11623,7 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
@@ -11671,7 +11636,7 @@
       </c>
       <c r="O213"/>
       <c r="P213" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q213"/>
     </row>
@@ -11707,7 +11672,7 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
@@ -11720,7 +11685,7 @@
       </c>
       <c r="O214"/>
       <c r="P214" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q214"/>
     </row>
@@ -11756,25 +11721,25 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N215" t="s">
         <v>32</v>
       </c>
       <c r="O215" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P215" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q215" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="216">
@@ -11809,25 +11774,25 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N216" t="s">
         <v>32</v>
       </c>
       <c r="O216" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P216" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q216" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
     <row r="217">
@@ -11862,25 +11827,25 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N217" t="s">
         <v>32</v>
       </c>
       <c r="O217" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P217" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q217" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e5", "e6", "e38", "e366", "e376", "e389", "e394", "e406", "e430", "e461", "e497", "e510", "e512")</t>
+    <t xml:space="preserve">c("e5", "e6", "e9", "e38", "e366", "e376", "e389", "e394", "e406", "e430", "e461", "e484", "e497", "e510", "e512", "e513")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e10", "e55", "e382", "e384", "e395", "e422", "e455", "e473", "e496")</t>
+    <t xml:space="preserve">c("e10", "e55", "e67", "e382", "e384", "e395", "e422", "e455", "e473", "e496")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 216, 217, 218, 219, 220, 266, 267, 268, 1899, 2230, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
   </si>
   <si>
     <t xml:space="preserve">c("e52", "e53", "e54", "e66", "e430", "e497")</t>
@@ -107,11 +107,11 @@
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 130, 131, 132, 140, 141, 142, 143, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
-2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
+2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e4", "e33", "e36", "e47", "e55", "e56", "e57", "e60", "e61", "e68", "e69", "e381", "e391", "e410", "e415", "e420", "e421", "e423", "e448", "e455", "e470", "e473", "e474", "e488", "e496", "e515", "e517")</t>
+    <t xml:space="preserve">c("e4", "e18", "e33", "e36", "e47", "e55", "e56", "e57", "e60", "e61", "e67", "e68", "e69", "e381", "e391", "e392", "e410", "e415", "e420", "e421", "e423", "e439", "e448", "e455", "e470", "e473", "e474", "e488", "e496", "e504", "e515", "e517")</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
@@ -135,49 +135,54 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 222, 224, 226, 228, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
+2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2289, 2290)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 248, 249, 250, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
+2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1773, 1824, 2054, 2056, 2058, 2289, 2290)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(177, 180, 229, 230, 231, 233, 234, 235, 236)</t>
+    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
@@ -186,7 +191,7 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2289, 2290)</t>
+    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
 </sst>
 </file>
@@ -612,13 +617,13 @@
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q2" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3">
@@ -665,13 +670,13 @@
         <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -718,13 +723,13 @@
         <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
@@ -771,13 +776,13 @@
         <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
@@ -824,13 +829,13 @@
         <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7">
@@ -877,13 +882,13 @@
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -933,10 +938,10 @@
         <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
@@ -986,10 +991,10 @@
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
@@ -1039,10 +1044,10 @@
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -1089,13 +1094,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q11" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="12">
@@ -1142,13 +1147,13 @@
         <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q12" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13">
@@ -1195,13 +1200,13 @@
         <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P13" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q13" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="14">
@@ -1248,13 +1253,13 @@
         <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q14" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15">
@@ -1301,13 +1306,13 @@
         <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q15" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16">
@@ -1354,13 +1359,13 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q16" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17">
@@ -1407,13 +1412,13 @@
         <v>26</v>
       </c>
       <c r="O17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q17" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18">
@@ -1460,13 +1465,13 @@
         <v>26</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19">
@@ -1513,13 +1518,13 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q19" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20">
@@ -1569,10 +1574,10 @@
         <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q20" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21">
@@ -1622,10 +1627,10 @@
         <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22">
@@ -1675,10 +1680,10 @@
         <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
@@ -1725,13 +1730,13 @@
         <v>32</v>
       </c>
       <c r="O23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P23" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q23" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="24">
@@ -1778,13 +1783,13 @@
         <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P24" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q24" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="25">
@@ -1831,13 +1836,13 @@
         <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P25" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q25" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="26">
@@ -1884,13 +1889,13 @@
         <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q26" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="27">
@@ -1937,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q27" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28">
@@ -1990,13 +1995,13 @@
         <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q28" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29">
@@ -2043,13 +2048,13 @@
         <v>26</v>
       </c>
       <c r="O29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P29" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q29" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30">
@@ -2096,13 +2101,13 @@
         <v>26</v>
       </c>
       <c r="O30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q30" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31">
@@ -2149,13 +2154,13 @@
         <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q31" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32">
@@ -2205,10 +2210,10 @@
         <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q32" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33">
@@ -2258,10 +2263,10 @@
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q33" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34">
@@ -2311,10 +2316,10 @@
         <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35">
@@ -2361,13 +2366,13 @@
         <v>32</v>
       </c>
       <c r="O35" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P35" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q35" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="36">
@@ -2414,13 +2419,13 @@
         <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P36" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q36" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="37">
@@ -2467,13 +2472,13 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P37" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q37" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="38">
@@ -2520,13 +2525,13 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q38" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39">
@@ -2573,13 +2578,13 @@
         <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q39" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40">
@@ -2626,13 +2631,13 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q40" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="41">
@@ -2679,13 +2684,13 @@
         <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q41" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42">
@@ -2732,13 +2737,13 @@
         <v>26</v>
       </c>
       <c r="O42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P42" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q42" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43">
@@ -2785,13 +2790,13 @@
         <v>26</v>
       </c>
       <c r="O43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q43" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44">
@@ -2841,10 +2846,10 @@
         <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q44" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
@@ -2894,10 +2899,10 @@
         <v>6</v>
       </c>
       <c r="P45" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q45" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46">
@@ -2947,10 +2952,10 @@
         <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q46" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47">
@@ -2997,13 +3002,13 @@
         <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P47" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q47" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="48">
@@ -3050,13 +3055,13 @@
         <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P48" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q48" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="49">
@@ -3103,13 +3108,13 @@
         <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P49" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q49" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="50">
@@ -3156,13 +3161,13 @@
         <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P50" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q50" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51">
@@ -3209,13 +3214,13 @@
         <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q51" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52">
@@ -3262,13 +3267,13 @@
         <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P52" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q52" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="53">
@@ -3315,13 +3320,13 @@
         <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P53" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q53" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54">
@@ -3368,13 +3373,13 @@
         <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q54" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55">
@@ -3421,13 +3426,13 @@
         <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q55" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56">
@@ -3477,10 +3482,10 @@
         <v>6</v>
       </c>
       <c r="P56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q56" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57">
@@ -3530,10 +3535,10 @@
         <v>6</v>
       </c>
       <c r="P57" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q57" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58">
@@ -3583,10 +3588,10 @@
         <v>6</v>
       </c>
       <c r="P58" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q58" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59">
@@ -3633,13 +3638,13 @@
         <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P59" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q59" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="60">
@@ -3686,13 +3691,13 @@
         <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P60" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q60" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="61">
@@ -3739,13 +3744,13 @@
         <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P61" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q61" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="62">
@@ -3792,13 +3797,13 @@
         <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P62" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q62" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63">
@@ -3845,13 +3850,13 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P63" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q63" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64">
@@ -3898,13 +3903,13 @@
         <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P64" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q64" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65">
@@ -3951,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="O65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q65" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66">
@@ -4004,13 +4009,13 @@
         <v>26</v>
       </c>
       <c r="O66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q66" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67">
@@ -4057,13 +4062,13 @@
         <v>26</v>
       </c>
       <c r="O67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P67" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q67" t="n">
-        <v>149</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68">
@@ -4113,10 +4118,10 @@
         <v>6</v>
       </c>
       <c r="P68" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q68" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69">
@@ -4166,10 +4171,10 @@
         <v>6</v>
       </c>
       <c r="P69" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q69" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70">
@@ -4219,10 +4224,10 @@
         <v>6</v>
       </c>
       <c r="P70" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q70" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71">
@@ -4269,13 +4274,13 @@
         <v>32</v>
       </c>
       <c r="O71" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P71" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q71" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="72">
@@ -4322,13 +4327,13 @@
         <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P72" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q72" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="73">
@@ -4375,13 +4380,13 @@
         <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P73" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="Q73" t="n">
-        <v>712</v>
+        <v>811</v>
       </c>
     </row>
     <row r="74">
@@ -4428,13 +4433,13 @@
         <v>22</v>
       </c>
       <c r="O74" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P74" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q74" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="75">
@@ -4481,13 +4486,13 @@
         <v>22</v>
       </c>
       <c r="O75" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P75" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q75" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76">
@@ -4534,13 +4539,13 @@
         <v>22</v>
       </c>
       <c r="O76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P76" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q76" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77">
@@ -4590,10 +4595,10 @@
         <v>7</v>
       </c>
       <c r="P77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q77" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78">
@@ -4643,10 +4648,10 @@
         <v>7</v>
       </c>
       <c r="P78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q78" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79">
@@ -4696,10 +4701,10 @@
         <v>7</v>
       </c>
       <c r="P79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q79" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80">
@@ -4749,10 +4754,10 @@
         <v>6</v>
       </c>
       <c r="P80" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q80" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81">
@@ -4802,10 +4807,10 @@
         <v>6</v>
       </c>
       <c r="P81" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q81" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82">
@@ -4855,10 +4860,10 @@
         <v>6</v>
       </c>
       <c r="P82" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q82" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83">
@@ -4905,13 +4910,13 @@
         <v>32</v>
       </c>
       <c r="O83" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P83" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="Q83" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
     </row>
     <row r="84">
@@ -4958,13 +4963,13 @@
         <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P84" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="Q84" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
     </row>
     <row r="85">
@@ -5011,13 +5016,13 @@
         <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P85" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="Q85" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
     </row>
     <row r="86">
@@ -5064,13 +5069,13 @@
         <v>22</v>
       </c>
       <c r="O86" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P86" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q86" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="87">
@@ -5117,13 +5122,13 @@
         <v>22</v>
       </c>
       <c r="O87" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P87" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q87" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="88">
@@ -5170,13 +5175,13 @@
         <v>22</v>
       </c>
       <c r="O88" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P88" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q88" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="89">
@@ -5226,10 +5231,10 @@
         <v>7</v>
       </c>
       <c r="P89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q89" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90">
@@ -5279,10 +5284,10 @@
         <v>7</v>
       </c>
       <c r="P90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q90" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91">
@@ -5332,10 +5337,10 @@
         <v>7</v>
       </c>
       <c r="P91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q91" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92">
@@ -5385,10 +5390,10 @@
         <v>6</v>
       </c>
       <c r="P92" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q92" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="93">
@@ -5438,10 +5443,10 @@
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q93" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="94">
@@ -5491,10 +5496,10 @@
         <v>6</v>
       </c>
       <c r="P94" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q94" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="95">
@@ -5541,13 +5546,13 @@
         <v>32</v>
       </c>
       <c r="O95" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P95" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="Q95" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96">
@@ -5594,13 +5599,13 @@
         <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P96" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="Q96" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
     </row>
     <row r="97">
@@ -5647,13 +5652,13 @@
         <v>32</v>
       </c>
       <c r="O97" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P97" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="Q97" t="n">
-        <v>424</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98">
@@ -5700,13 +5705,13 @@
         <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P98" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q98" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="99">
@@ -5753,13 +5758,13 @@
         <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P99" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q99" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100">
@@ -5806,13 +5811,13 @@
         <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P100" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q100" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="101">
@@ -5859,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="O101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P101" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q101" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="102">
@@ -5912,13 +5917,13 @@
         <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P102" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q102" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103">
@@ -5965,13 +5970,13 @@
         <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q103" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104">
@@ -6021,10 +6026,10 @@
         <v>6</v>
       </c>
       <c r="P104" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q104" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105">
@@ -6074,10 +6079,10 @@
         <v>6</v>
       </c>
       <c r="P105" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q105" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="106">
@@ -6127,10 +6132,10 @@
         <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q106" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="107">
@@ -6177,13 +6182,13 @@
         <v>32</v>
       </c>
       <c r="O107" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P107" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="Q107" t="n">
-        <v>629</v>
+        <v>728</v>
       </c>
     </row>
     <row r="108">
@@ -6230,13 +6235,13 @@
         <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P108" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="Q108" t="n">
-        <v>629</v>
+        <v>728</v>
       </c>
     </row>
     <row r="109">
@@ -6283,13 +6288,13 @@
         <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P109" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="Q109" t="n">
-        <v>629</v>
+        <v>728</v>
       </c>
     </row>
     <row r="110">
@@ -6336,13 +6341,13 @@
         <v>22</v>
       </c>
       <c r="O110" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P110" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q110" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="111">
@@ -6389,13 +6394,13 @@
         <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P111" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q111" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112">
@@ -6442,13 +6447,13 @@
         <v>22</v>
       </c>
       <c r="O112" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P112" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="Q112" t="n">
-        <v>252</v>
+        <v>395</v>
       </c>
     </row>
     <row r="113">
@@ -6495,13 +6500,13 @@
         <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P113" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q113" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="114">
@@ -6548,13 +6553,13 @@
         <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P114" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q114" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="115">
@@ -6601,13 +6606,13 @@
         <v>26</v>
       </c>
       <c r="O115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P115" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q115" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="116">
@@ -6657,10 +6662,10 @@
         <v>6</v>
       </c>
       <c r="P116" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q116" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="117">
@@ -6710,10 +6715,10 @@
         <v>6</v>
       </c>
       <c r="P117" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q117" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118">
@@ -6763,10 +6768,10 @@
         <v>6</v>
       </c>
       <c r="P118" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q118" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="119">
@@ -6813,13 +6818,13 @@
         <v>32</v>
       </c>
       <c r="O119" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P119" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="Q119" t="n">
-        <v>629</v>
+        <v>728</v>
       </c>
     </row>
     <row r="120">
@@ -6866,13 +6871,13 @@
         <v>32</v>
       </c>
       <c r="O120" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P120" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="Q120" t="n">
-        <v>629</v>
+        <v>728</v>
       </c>
     </row>
     <row r="121">
@@ -6919,13 +6924,13 @@
         <v>32</v>
       </c>
       <c r="O121" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P121" t="n">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="Q121" t="n">
-        <v>629</v>
+        <v>728</v>
       </c>
     </row>
     <row r="122">
@@ -6972,13 +6977,13 @@
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P122" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q122" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123">
@@ -7025,13 +7030,13 @@
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P123" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q123" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124">
@@ -7078,13 +7083,13 @@
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P124" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q124" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="125">
@@ -7131,13 +7136,13 @@
         <v>26</v>
       </c>
       <c r="O125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P125" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q125" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126">
@@ -7184,13 +7189,13 @@
         <v>26</v>
       </c>
       <c r="O126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P126" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q126" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="127">
@@ -7237,13 +7242,13 @@
         <v>26</v>
       </c>
       <c r="O127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P127" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q127" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="128">
@@ -7251,7 +7256,7 @@
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
@@ -7284,23 +7289,27 @@
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
       </c>
-      <c r="O128"/>
+      <c r="O128" t="n">
+        <v>3</v>
+      </c>
       <c r="P128" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q128"/>
+        <v>7</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -7333,23 +7342,27 @@
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
       </c>
-      <c r="O129"/>
+      <c r="O129" t="n">
+        <v>3</v>
+      </c>
       <c r="P129" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q129"/>
+        <v>7</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -7382,16 +7395,20 @@
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
       </c>
-      <c r="O130"/>
+      <c r="O130" t="n">
+        <v>3</v>
+      </c>
       <c r="P130" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q130"/>
+        <v>7</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7431,19 +7448,19 @@
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N131" t="s">
         <v>32</v>
       </c>
       <c r="O131" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P131" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Q131" t="n">
-        <v>607</v>
+        <v>702</v>
       </c>
     </row>
     <row r="132">
@@ -7484,19 +7501,19 @@
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N132" t="s">
         <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P132" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Q132" t="n">
-        <v>607</v>
+        <v>702</v>
       </c>
     </row>
     <row r="133">
@@ -7537,19 +7554,19 @@
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N133" t="s">
         <v>32</v>
       </c>
       <c r="O133" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P133" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Q133" t="n">
-        <v>607</v>
+        <v>702</v>
       </c>
     </row>
     <row r="134">
@@ -7596,13 +7613,13 @@
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P134" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q134" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="135">
@@ -7649,13 +7666,13 @@
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P135" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q135" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="136">
@@ -7702,13 +7719,13 @@
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P136" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q136" t="n">
-        <v>206</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137">
@@ -7755,13 +7772,13 @@
         <v>26</v>
       </c>
       <c r="O137" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P137" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q137" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="138">
@@ -7808,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="O138" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P138" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q138" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="139">
@@ -7861,13 +7878,13 @@
         <v>26</v>
       </c>
       <c r="O139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P139" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q139" t="n">
-        <v>133</v>
+        <v>161</v>
       </c>
     </row>
     <row r="140">
@@ -7908,16 +7925,20 @@
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
       </c>
-      <c r="O140"/>
+      <c r="O140" t="n">
+        <v>3</v>
+      </c>
       <c r="P140" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q140"/>
+        <v>7</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7957,16 +7978,20 @@
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
       </c>
-      <c r="O141"/>
+      <c r="O141" t="n">
+        <v>3</v>
+      </c>
       <c r="P141" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q141"/>
+        <v>7</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8006,16 +8031,20 @@
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
       </c>
-      <c r="O142"/>
+      <c r="O142" t="n">
+        <v>3</v>
+      </c>
       <c r="P142" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q142"/>
+        <v>7</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8055,19 +8084,19 @@
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N143" t="s">
         <v>32</v>
       </c>
       <c r="O143" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P143" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Q143" t="n">
-        <v>607</v>
+        <v>702</v>
       </c>
     </row>
     <row r="144">
@@ -8108,19 +8137,19 @@
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N144" t="s">
         <v>32</v>
       </c>
       <c r="O144" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P144" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Q144" t="n">
-        <v>607</v>
+        <v>702</v>
       </c>
     </row>
     <row r="145">
@@ -8161,19 +8190,19 @@
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N145" t="s">
         <v>32</v>
       </c>
       <c r="O145" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P145" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Q145" t="n">
-        <v>607</v>
+        <v>702</v>
       </c>
     </row>
     <row r="146">
@@ -8208,25 +8237,25 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N146" t="s">
         <v>22</v>
       </c>
       <c r="O146" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P146" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q146" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="147">
@@ -8261,25 +8290,25 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N147" t="s">
         <v>22</v>
       </c>
       <c r="O147" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P147" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q147" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="148">
@@ -8314,25 +8343,25 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N148" t="s">
         <v>22</v>
       </c>
       <c r="O148" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P148" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q148" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="149">
@@ -8367,7 +8396,7 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
@@ -8380,7 +8409,7 @@
       </c>
       <c r="O149"/>
       <c r="P149" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q149"/>
     </row>
@@ -8416,7 +8445,7 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
@@ -8429,7 +8458,7 @@
       </c>
       <c r="O150"/>
       <c r="P150" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q150"/>
     </row>
@@ -8465,7 +8494,7 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
@@ -8478,7 +8507,7 @@
       </c>
       <c r="O151"/>
       <c r="P151" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q151"/>
     </row>
@@ -8514,7 +8543,7 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
@@ -8527,7 +8556,7 @@
       </c>
       <c r="O152"/>
       <c r="P152" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q152"/>
     </row>
@@ -8563,7 +8592,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
@@ -8576,7 +8605,7 @@
       </c>
       <c r="O153"/>
       <c r="P153" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q153"/>
     </row>
@@ -8612,7 +8641,7 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
@@ -8625,7 +8654,7 @@
       </c>
       <c r="O154"/>
       <c r="P154" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q154"/>
     </row>
@@ -8661,25 +8690,25 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N155" t="s">
         <v>32</v>
       </c>
       <c r="O155" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P155" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q155" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156">
@@ -8714,25 +8743,25 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N156" t="s">
         <v>32</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P156" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q156" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157">
@@ -8767,25 +8796,25 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N157" t="s">
         <v>32</v>
       </c>
       <c r="O157" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P157" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q157" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158">
@@ -8820,25 +8849,25 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N158" t="s">
         <v>22</v>
       </c>
       <c r="O158" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P158" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q158" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="159">
@@ -8873,25 +8902,25 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N159" t="s">
         <v>22</v>
       </c>
       <c r="O159" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P159" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q159" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="160">
@@ -8926,25 +8955,25 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N160" t="s">
         <v>22</v>
       </c>
       <c r="O160" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P160" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q160" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="161">
@@ -8979,7 +9008,7 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
@@ -8992,7 +9021,7 @@
       </c>
       <c r="O161"/>
       <c r="P161" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q161"/>
     </row>
@@ -9028,7 +9057,7 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
@@ -9041,7 +9070,7 @@
       </c>
       <c r="O162"/>
       <c r="P162" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q162"/>
     </row>
@@ -9077,7 +9106,7 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
@@ -9090,7 +9119,7 @@
       </c>
       <c r="O163"/>
       <c r="P163" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q163"/>
     </row>
@@ -9126,7 +9155,7 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
@@ -9139,7 +9168,7 @@
       </c>
       <c r="O164"/>
       <c r="P164" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q164"/>
     </row>
@@ -9175,7 +9204,7 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
@@ -9188,7 +9217,7 @@
       </c>
       <c r="O165"/>
       <c r="P165" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q165"/>
     </row>
@@ -9224,7 +9253,7 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9237,7 +9266,7 @@
       </c>
       <c r="O166"/>
       <c r="P166" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q166"/>
     </row>
@@ -9273,25 +9302,25 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N167" t="s">
         <v>32</v>
       </c>
       <c r="O167" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P167" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q167" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168">
@@ -9326,25 +9355,25 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N168" t="s">
         <v>32</v>
       </c>
       <c r="O168" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P168" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q168" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169">
@@ -9379,25 +9408,25 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N169" t="s">
         <v>32</v>
       </c>
       <c r="O169" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P169" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q169" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170">
@@ -9432,25 +9461,25 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N170" t="s">
         <v>22</v>
       </c>
       <c r="O170" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P170" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q170" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="171">
@@ -9485,25 +9514,25 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N171" t="s">
         <v>22</v>
       </c>
       <c r="O171" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P171" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q171" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="172">
@@ -9538,25 +9567,25 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N172" t="s">
         <v>22</v>
       </c>
       <c r="O172" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P172" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q172" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="173">
@@ -9591,7 +9620,7 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
@@ -9604,7 +9633,7 @@
       </c>
       <c r="O173"/>
       <c r="P173" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q173"/>
     </row>
@@ -9640,7 +9669,7 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
@@ -9653,7 +9682,7 @@
       </c>
       <c r="O174"/>
       <c r="P174" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q174"/>
     </row>
@@ -9689,7 +9718,7 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
@@ -9702,7 +9731,7 @@
       </c>
       <c r="O175"/>
       <c r="P175" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q175"/>
     </row>
@@ -9738,7 +9767,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -9751,7 +9780,7 @@
       </c>
       <c r="O176"/>
       <c r="P176" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q176"/>
     </row>
@@ -9787,7 +9816,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
@@ -9800,7 +9829,7 @@
       </c>
       <c r="O177"/>
       <c r="P177" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q177"/>
     </row>
@@ -9836,7 +9865,7 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
@@ -9849,7 +9878,7 @@
       </c>
       <c r="O178"/>
       <c r="P178" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q178"/>
     </row>
@@ -9885,25 +9914,25 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N179" t="s">
         <v>32</v>
       </c>
       <c r="O179" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P179" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q179" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180">
@@ -9938,25 +9967,25 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N180" t="s">
         <v>32</v>
       </c>
       <c r="O180" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P180" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q180" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181">
@@ -9991,25 +10020,25 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N181" t="s">
         <v>32</v>
       </c>
       <c r="O181" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P181" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q181" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182">
@@ -10044,25 +10073,25 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N182" t="s">
         <v>22</v>
       </c>
       <c r="O182" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P182" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q182" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="183">
@@ -10097,25 +10126,25 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N183" t="s">
         <v>22</v>
       </c>
       <c r="O183" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P183" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q183" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="184">
@@ -10150,25 +10179,25 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N184" t="s">
         <v>22</v>
       </c>
       <c r="O184" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P184" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q184" t="n">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="185">
@@ -10203,7 +10232,7 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
@@ -10216,7 +10245,7 @@
       </c>
       <c r="O185"/>
       <c r="P185" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q185"/>
     </row>
@@ -10252,7 +10281,7 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
@@ -10265,7 +10294,7 @@
       </c>
       <c r="O186"/>
       <c r="P186" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q186"/>
     </row>
@@ -10301,7 +10330,7 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
@@ -10314,7 +10343,7 @@
       </c>
       <c r="O187"/>
       <c r="P187" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q187"/>
     </row>
@@ -10350,7 +10379,7 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
@@ -10363,7 +10392,7 @@
       </c>
       <c r="O188"/>
       <c r="P188" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q188"/>
     </row>
@@ -10399,7 +10428,7 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
@@ -10412,7 +10441,7 @@
       </c>
       <c r="O189"/>
       <c r="P189" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q189"/>
     </row>
@@ -10448,7 +10477,7 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
@@ -10461,7 +10490,7 @@
       </c>
       <c r="O190"/>
       <c r="P190" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q190"/>
     </row>
@@ -10497,25 +10526,25 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N191" t="s">
         <v>32</v>
       </c>
       <c r="O191" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P191" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q191" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192">
@@ -10550,25 +10579,25 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N192" t="s">
         <v>32</v>
       </c>
       <c r="O192" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P192" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q192" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193">
@@ -10603,25 +10632,25 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N193" t="s">
         <v>32</v>
       </c>
       <c r="O193" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P193" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q193" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194">
@@ -10656,25 +10685,25 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N194" t="s">
         <v>22</v>
       </c>
       <c r="O194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P194" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q194" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="195">
@@ -10709,25 +10738,25 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N195" t="s">
         <v>22</v>
       </c>
       <c r="O195" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P195" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q195" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="196">
@@ -10762,25 +10791,25 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N196" t="s">
         <v>22</v>
       </c>
       <c r="O196" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P196" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q196" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="197">
@@ -10815,7 +10844,7 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
@@ -10828,7 +10857,7 @@
       </c>
       <c r="O197"/>
       <c r="P197" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q197"/>
     </row>
@@ -10864,7 +10893,7 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
@@ -10877,7 +10906,7 @@
       </c>
       <c r="O198"/>
       <c r="P198" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q198"/>
     </row>
@@ -10913,7 +10942,7 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
@@ -10926,7 +10955,7 @@
       </c>
       <c r="O199"/>
       <c r="P199" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q199"/>
     </row>
@@ -10962,7 +10991,7 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
@@ -10975,7 +11004,7 @@
       </c>
       <c r="O200"/>
       <c r="P200" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q200"/>
     </row>
@@ -11011,7 +11040,7 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
@@ -11024,7 +11053,7 @@
       </c>
       <c r="O201"/>
       <c r="P201" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q201"/>
     </row>
@@ -11060,7 +11089,7 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
@@ -11073,7 +11102,7 @@
       </c>
       <c r="O202"/>
       <c r="P202" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q202"/>
     </row>
@@ -11109,25 +11138,25 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N203" t="s">
         <v>32</v>
       </c>
       <c r="O203" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P203" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q203" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204">
@@ -11162,25 +11191,25 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N204" t="s">
         <v>32</v>
       </c>
       <c r="O204" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P204" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q204" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205">
@@ -11215,25 +11244,25 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N205" t="s">
         <v>32</v>
       </c>
       <c r="O205" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P205" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q205" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206">
@@ -11268,25 +11297,25 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N206" t="s">
         <v>22</v>
       </c>
       <c r="O206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P206" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q206" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="207">
@@ -11321,25 +11350,25 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N207" t="s">
         <v>22</v>
       </c>
       <c r="O207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P207" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q207" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="208">
@@ -11374,25 +11403,25 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N208" t="s">
         <v>22</v>
       </c>
       <c r="O208" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P208" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q208" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
     </row>
     <row r="209">
@@ -11427,7 +11456,7 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
@@ -11440,7 +11469,7 @@
       </c>
       <c r="O209"/>
       <c r="P209" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q209"/>
     </row>
@@ -11476,7 +11505,7 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
@@ -11489,7 +11518,7 @@
       </c>
       <c r="O210"/>
       <c r="P210" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q210"/>
     </row>
@@ -11525,7 +11554,7 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
@@ -11538,7 +11567,7 @@
       </c>
       <c r="O211"/>
       <c r="P211" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q211"/>
     </row>
@@ -11574,7 +11603,7 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
@@ -11587,7 +11616,7 @@
       </c>
       <c r="O212"/>
       <c r="P212" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q212"/>
     </row>
@@ -11623,7 +11652,7 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
@@ -11636,7 +11665,7 @@
       </c>
       <c r="O213"/>
       <c r="P213" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q213"/>
     </row>
@@ -11672,7 +11701,7 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
@@ -11685,7 +11714,7 @@
       </c>
       <c r="O214"/>
       <c r="P214" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q214"/>
     </row>
@@ -11721,25 +11750,25 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N215" t="s">
         <v>32</v>
       </c>
       <c r="O215" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P215" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q215" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216">
@@ -11774,25 +11803,25 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N216" t="s">
         <v>32</v>
       </c>
       <c r="O216" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P216" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q216" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217">
@@ -11827,25 +11856,25 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N217" t="s">
         <v>32</v>
       </c>
       <c r="O217" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P217" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Q217" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
@@ -126,16 +126,19 @@
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
@@ -144,10 +147,10 @@
     <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
@@ -157,41 +160,17 @@
 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1897, 1898, 1900, 2054, 2056, 2058, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(265, 266, 267, 268, 1899, 2230, 2232)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
-2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + EE_nutrition</t>
   </si>
   <si>
     <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 229, 230, 231, 233, 234, 235, 236, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 2054, 2056, 2058, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
+2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
 </sst>
 </file>
@@ -1877,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1930,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -1983,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2195,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2248,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2301,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2513,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2566,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2619,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2831,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2884,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -2937,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -3149,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3202,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3255,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3308,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3361,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3414,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3467,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3520,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3573,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3626,7 +3605,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3679,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3732,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3785,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3838,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3891,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3944,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3997,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -4050,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4103,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4156,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4209,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4262,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4315,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4368,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4421,7 +4400,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4474,7 +4453,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4527,7 +4506,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4580,13 +4559,13 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
@@ -4633,13 +4612,13 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
@@ -4686,13 +4665,13 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
@@ -4739,7 +4718,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4792,7 +4771,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4845,7 +4824,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4898,13 +4877,13 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N83" t="s">
         <v>32</v>
@@ -4951,13 +4930,13 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N84" t="s">
         <v>32</v>
@@ -5004,13 +4983,13 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N85" t="s">
         <v>32</v>
@@ -5057,7 +5036,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5110,7 +5089,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5163,7 +5142,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5216,13 +5195,13 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
@@ -5269,13 +5248,13 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
@@ -5322,13 +5301,13 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
@@ -5375,7 +5354,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5428,7 +5407,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5481,7 +5460,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5534,13 +5513,13 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N95" t="s">
         <v>32</v>
@@ -5587,13 +5566,13 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N96" t="s">
         <v>32</v>
@@ -5640,13 +5619,13 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
@@ -5693,7 +5672,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -5746,7 +5725,7 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
@@ -5799,7 +5778,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
@@ -5852,13 +5831,13 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N101" t="s">
         <v>26</v>
@@ -5905,13 +5884,13 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N102" t="s">
         <v>26</v>
@@ -5958,13 +5937,13 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N103" t="s">
         <v>26</v>
@@ -6011,7 +5990,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6064,7 +6043,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6117,7 +6096,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6170,13 +6149,13 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
@@ -6223,13 +6202,13 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
@@ -6276,13 +6255,13 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N109" t="s">
         <v>32</v>
@@ -6329,7 +6308,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -6382,7 +6361,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
@@ -6435,7 +6414,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
@@ -6488,13 +6467,13 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N113" t="s">
         <v>26</v>
@@ -6541,13 +6520,13 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N114" t="s">
         <v>26</v>
@@ -6594,13 +6573,13 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N115" t="s">
         <v>26</v>
@@ -6647,7 +6626,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6700,7 +6679,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6753,7 +6732,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6806,13 +6785,13 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
@@ -6859,13 +6838,13 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
@@ -6912,13 +6891,13 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
@@ -6965,25 +6944,25 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P122" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q122" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
     </row>
     <row r="123">
@@ -7018,25 +6997,25 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P123" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q123" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124">
@@ -7071,25 +7050,25 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P124" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q124" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
     </row>
     <row r="125">
@@ -7124,13 +7103,13 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N125" t="s">
         <v>26</v>
@@ -7177,13 +7156,13 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N126" t="s">
         <v>26</v>
@@ -7230,13 +7209,13 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N127" t="s">
         <v>26</v>
@@ -7256,7 +7235,7 @@
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
@@ -7283,33 +7262,29 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
       </c>
-      <c r="O128" t="n">
-        <v>3</v>
-      </c>
+      <c r="O128"/>
       <c r="P128" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q128"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -7336,33 +7311,29 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
       </c>
-      <c r="O129" t="n">
-        <v>3</v>
-      </c>
+      <c r="O129"/>
       <c r="P129" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q129"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -7389,26 +7360,22 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
       </c>
-      <c r="O130" t="n">
-        <v>3</v>
-      </c>
+      <c r="O130"/>
       <c r="P130" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q130"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7442,7 +7409,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -7495,7 +7462,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
@@ -7548,7 +7515,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7601,25 +7568,25 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P134" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q134" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
     </row>
     <row r="135">
@@ -7654,25 +7621,25 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P135" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q135" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
     </row>
     <row r="136">
@@ -7707,25 +7674,25 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P136" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q136" t="n">
-        <v>251</v>
+        <v>298</v>
       </c>
     </row>
     <row r="137">
@@ -7760,13 +7727,13 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N137" t="s">
         <v>26</v>
@@ -7813,13 +7780,13 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N138" t="s">
         <v>26</v>
@@ -7866,13 +7833,13 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N139" t="s">
         <v>26</v>
@@ -7919,26 +7886,22 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
       </c>
-      <c r="O140" t="n">
-        <v>3</v>
-      </c>
+      <c r="O140"/>
       <c r="P140" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q140"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7972,26 +7935,22 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
       </c>
-      <c r="O141" t="n">
-        <v>3</v>
-      </c>
+      <c r="O141"/>
       <c r="P141" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q141"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8025,26 +7984,22 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
       </c>
-      <c r="O142" t="n">
-        <v>3</v>
-      </c>
+      <c r="O142"/>
       <c r="P142" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>62</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="Q142"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8078,7 +8033,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
@@ -8131,7 +8086,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
@@ -8184,7 +8139,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -8203,3678 +8158,6 @@
       </c>
       <c r="Q145" t="n">
         <v>702</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>292</v>
-      </c>
-      <c r="B146" t="b">
-        <v>0</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>18</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>19</v>
-      </c>
-      <c r="I146" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>3</v>
-      </c>
-      <c r="K146" t="s">
-        <v>52</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="s">
-        <v>53</v>
-      </c>
-      <c r="N146" t="s">
-        <v>22</v>
-      </c>
-      <c r="O146" t="n">
-        <v>11</v>
-      </c>
-      <c r="P146" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>293</v>
-      </c>
-      <c r="B147" t="b">
-        <v>0</v>
-      </c>
-      <c r="C147" t="s">
-        <v>17</v>
-      </c>
-      <c r="D147" t="s">
-        <v>18</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" t="s">
-        <v>19</v>
-      </c>
-      <c r="I147" t="n">
-        <v>7</v>
-      </c>
-      <c r="J147" t="n">
-        <v>3</v>
-      </c>
-      <c r="K147" t="s">
-        <v>52</v>
-      </c>
-      <c r="L147" t="n">
-        <v>2</v>
-      </c>
-      <c r="M147" t="s">
-        <v>53</v>
-      </c>
-      <c r="N147" t="s">
-        <v>22</v>
-      </c>
-      <c r="O147" t="n">
-        <v>11</v>
-      </c>
-      <c r="P147" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>294</v>
-      </c>
-      <c r="B148" t="b">
-        <v>0</v>
-      </c>
-      <c r="C148" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" t="s">
-        <v>18</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="s">
-        <v>19</v>
-      </c>
-      <c r="I148" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="s">
-        <v>52</v>
-      </c>
-      <c r="L148" t="n">
-        <v>3</v>
-      </c>
-      <c r="M148" t="s">
-        <v>53</v>
-      </c>
-      <c r="N148" t="s">
-        <v>22</v>
-      </c>
-      <c r="O148" t="n">
-        <v>11</v>
-      </c>
-      <c r="P148" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>298</v>
-      </c>
-      <c r="B149" t="b">
-        <v>1</v>
-      </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" t="s">
-        <v>18</v>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="n">
-        <v>2</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" t="s">
-        <v>23</v>
-      </c>
-      <c r="I149" t="n">
-        <v>7</v>
-      </c>
-      <c r="J149" t="n">
-        <v>3</v>
-      </c>
-      <c r="K149" t="s">
-        <v>54</v>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="s">
-        <v>25</v>
-      </c>
-      <c r="N149" t="s">
-        <v>26</v>
-      </c>
-      <c r="O149"/>
-      <c r="P149" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q149"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>299</v>
-      </c>
-      <c r="B150" t="b">
-        <v>1</v>
-      </c>
-      <c r="C150" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" t="s">
-        <v>18</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" t="s">
-        <v>23</v>
-      </c>
-      <c r="I150" t="n">
-        <v>7</v>
-      </c>
-      <c r="J150" t="n">
-        <v>3</v>
-      </c>
-      <c r="K150" t="s">
-        <v>54</v>
-      </c>
-      <c r="L150" t="n">
-        <v>2</v>
-      </c>
-      <c r="M150" t="s">
-        <v>25</v>
-      </c>
-      <c r="N150" t="s">
-        <v>26</v>
-      </c>
-      <c r="O150"/>
-      <c r="P150" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q150"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>300</v>
-      </c>
-      <c r="B151" t="b">
-        <v>1</v>
-      </c>
-      <c r="C151" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" t="s">
-        <v>18</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="n">
-        <v>2</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" t="s">
-        <v>23</v>
-      </c>
-      <c r="I151" t="n">
-        <v>7</v>
-      </c>
-      <c r="J151" t="n">
-        <v>3</v>
-      </c>
-      <c r="K151" t="s">
-        <v>54</v>
-      </c>
-      <c r="L151" t="n">
-        <v>3</v>
-      </c>
-      <c r="M151" t="s">
-        <v>25</v>
-      </c>
-      <c r="N151" t="s">
-        <v>26</v>
-      </c>
-      <c r="O151"/>
-      <c r="P151" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q151"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>304</v>
-      </c>
-      <c r="B152" t="b">
-        <v>1</v>
-      </c>
-      <c r="C152" t="s">
-        <v>17</v>
-      </c>
-      <c r="D152" t="s">
-        <v>18</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="s">
-        <v>27</v>
-      </c>
-      <c r="I152" t="n">
-        <v>7</v>
-      </c>
-      <c r="J152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="s">
-        <v>52</v>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="s">
-        <v>28</v>
-      </c>
-      <c r="N152" t="s">
-        <v>29</v>
-      </c>
-      <c r="O152"/>
-      <c r="P152" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q152"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>305</v>
-      </c>
-      <c r="B153" t="b">
-        <v>1</v>
-      </c>
-      <c r="C153" t="s">
-        <v>17</v>
-      </c>
-      <c r="D153" t="s">
-        <v>18</v>
-      </c>
-      <c r="E153" t="n">
-        <v>2</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="s">
-        <v>27</v>
-      </c>
-      <c r="I153" t="n">
-        <v>7</v>
-      </c>
-      <c r="J153" t="n">
-        <v>3</v>
-      </c>
-      <c r="K153" t="s">
-        <v>52</v>
-      </c>
-      <c r="L153" t="n">
-        <v>2</v>
-      </c>
-      <c r="M153" t="s">
-        <v>28</v>
-      </c>
-      <c r="N153" t="s">
-        <v>29</v>
-      </c>
-      <c r="O153"/>
-      <c r="P153" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q153"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>306</v>
-      </c>
-      <c r="B154" t="b">
-        <v>1</v>
-      </c>
-      <c r="C154" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" t="s">
-        <v>18</v>
-      </c>
-      <c r="E154" t="n">
-        <v>2</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="s">
-        <v>27</v>
-      </c>
-      <c r="I154" t="n">
-        <v>7</v>
-      </c>
-      <c r="J154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" t="s">
-        <v>52</v>
-      </c>
-      <c r="L154" t="n">
-        <v>3</v>
-      </c>
-      <c r="M154" t="s">
-        <v>28</v>
-      </c>
-      <c r="N154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O154"/>
-      <c r="P154" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q154"/>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>310</v>
-      </c>
-      <c r="B155" t="b">
-        <v>0</v>
-      </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>18</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-      <c r="F155" t="n">
-        <v>2</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="s">
-        <v>30</v>
-      </c>
-      <c r="I155" t="n">
-        <v>7</v>
-      </c>
-      <c r="J155" t="n">
-        <v>3</v>
-      </c>
-      <c r="K155" t="s">
-        <v>54</v>
-      </c>
-      <c r="L155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M155" t="s">
-        <v>55</v>
-      </c>
-      <c r="N155" t="s">
-        <v>32</v>
-      </c>
-      <c r="O155" t="n">
-        <v>7</v>
-      </c>
-      <c r="P155" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>311</v>
-      </c>
-      <c r="B156" t="b">
-        <v>0</v>
-      </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" t="s">
-        <v>18</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="s">
-        <v>30</v>
-      </c>
-      <c r="I156" t="n">
-        <v>7</v>
-      </c>
-      <c r="J156" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" t="s">
-        <v>54</v>
-      </c>
-      <c r="L156" t="n">
-        <v>2</v>
-      </c>
-      <c r="M156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N156" t="s">
-        <v>32</v>
-      </c>
-      <c r="O156" t="n">
-        <v>7</v>
-      </c>
-      <c r="P156" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>312</v>
-      </c>
-      <c r="B157" t="b">
-        <v>0</v>
-      </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
-      <c r="D157" t="s">
-        <v>18</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2</v>
-      </c>
-      <c r="F157" t="n">
-        <v>2</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="s">
-        <v>30</v>
-      </c>
-      <c r="I157" t="n">
-        <v>7</v>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" t="s">
-        <v>54</v>
-      </c>
-      <c r="L157" t="n">
-        <v>3</v>
-      </c>
-      <c r="M157" t="s">
-        <v>55</v>
-      </c>
-      <c r="N157" t="s">
-        <v>32</v>
-      </c>
-      <c r="O157" t="n">
-        <v>7</v>
-      </c>
-      <c r="P157" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>316</v>
-      </c>
-      <c r="B158" t="b">
-        <v>0</v>
-      </c>
-      <c r="C158" t="s">
-        <v>17</v>
-      </c>
-      <c r="D158" t="s">
-        <v>18</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2</v>
-      </c>
-      <c r="H158" t="s">
-        <v>33</v>
-      </c>
-      <c r="I158" t="n">
-        <v>7</v>
-      </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="s">
-        <v>52</v>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="s">
-        <v>53</v>
-      </c>
-      <c r="N158" t="s">
-        <v>22</v>
-      </c>
-      <c r="O158" t="n">
-        <v>11</v>
-      </c>
-      <c r="P158" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>317</v>
-      </c>
-      <c r="B159" t="b">
-        <v>0</v>
-      </c>
-      <c r="C159" t="s">
-        <v>17</v>
-      </c>
-      <c r="D159" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" t="n">
-        <v>2</v>
-      </c>
-      <c r="H159" t="s">
-        <v>33</v>
-      </c>
-      <c r="I159" t="n">
-        <v>7</v>
-      </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="s">
-        <v>52</v>
-      </c>
-      <c r="L159" t="n">
-        <v>2</v>
-      </c>
-      <c r="M159" t="s">
-        <v>53</v>
-      </c>
-      <c r="N159" t="s">
-        <v>22</v>
-      </c>
-      <c r="O159" t="n">
-        <v>11</v>
-      </c>
-      <c r="P159" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>318</v>
-      </c>
-      <c r="B160" t="b">
-        <v>0</v>
-      </c>
-      <c r="C160" t="s">
-        <v>17</v>
-      </c>
-      <c r="D160" t="s">
-        <v>18</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="n">
-        <v>2</v>
-      </c>
-      <c r="H160" t="s">
-        <v>33</v>
-      </c>
-      <c r="I160" t="n">
-        <v>7</v>
-      </c>
-      <c r="J160" t="n">
-        <v>3</v>
-      </c>
-      <c r="K160" t="s">
-        <v>52</v>
-      </c>
-      <c r="L160" t="n">
-        <v>3</v>
-      </c>
-      <c r="M160" t="s">
-        <v>53</v>
-      </c>
-      <c r="N160" t="s">
-        <v>22</v>
-      </c>
-      <c r="O160" t="n">
-        <v>11</v>
-      </c>
-      <c r="P160" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>322</v>
-      </c>
-      <c r="B161" t="b">
-        <v>1</v>
-      </c>
-      <c r="C161" t="s">
-        <v>17</v>
-      </c>
-      <c r="D161" t="s">
-        <v>18</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" t="n">
-        <v>2</v>
-      </c>
-      <c r="G161" t="n">
-        <v>2</v>
-      </c>
-      <c r="H161" t="s">
-        <v>34</v>
-      </c>
-      <c r="I161" t="n">
-        <v>7</v>
-      </c>
-      <c r="J161" t="n">
-        <v>3</v>
-      </c>
-      <c r="K161" t="s">
-        <v>54</v>
-      </c>
-      <c r="L161" t="n">
-        <v>1</v>
-      </c>
-      <c r="M161" t="s">
-        <v>25</v>
-      </c>
-      <c r="N161" t="s">
-        <v>26</v>
-      </c>
-      <c r="O161"/>
-      <c r="P161" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q161"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>323</v>
-      </c>
-      <c r="B162" t="b">
-        <v>1</v>
-      </c>
-      <c r="C162" t="s">
-        <v>17</v>
-      </c>
-      <c r="D162" t="s">
-        <v>18</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" t="n">
-        <v>2</v>
-      </c>
-      <c r="H162" t="s">
-        <v>34</v>
-      </c>
-      <c r="I162" t="n">
-        <v>7</v>
-      </c>
-      <c r="J162" t="n">
-        <v>3</v>
-      </c>
-      <c r="K162" t="s">
-        <v>54</v>
-      </c>
-      <c r="L162" t="n">
-        <v>2</v>
-      </c>
-      <c r="M162" t="s">
-        <v>25</v>
-      </c>
-      <c r="N162" t="s">
-        <v>26</v>
-      </c>
-      <c r="O162"/>
-      <c r="P162" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q162"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>324</v>
-      </c>
-      <c r="B163" t="b">
-        <v>1</v>
-      </c>
-      <c r="C163" t="s">
-        <v>17</v>
-      </c>
-      <c r="D163" t="s">
-        <v>18</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>2</v>
-      </c>
-      <c r="G163" t="n">
-        <v>2</v>
-      </c>
-      <c r="H163" t="s">
-        <v>34</v>
-      </c>
-      <c r="I163" t="n">
-        <v>7</v>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
-      <c r="K163" t="s">
-        <v>54</v>
-      </c>
-      <c r="L163" t="n">
-        <v>3</v>
-      </c>
-      <c r="M163" t="s">
-        <v>25</v>
-      </c>
-      <c r="N163" t="s">
-        <v>26</v>
-      </c>
-      <c r="O163"/>
-      <c r="P163" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q163"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>328</v>
-      </c>
-      <c r="B164" t="b">
-        <v>1</v>
-      </c>
-      <c r="C164" t="s">
-        <v>17</v>
-      </c>
-      <c r="D164" t="s">
-        <v>18</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" t="n">
-        <v>2</v>
-      </c>
-      <c r="H164" t="s">
-        <v>35</v>
-      </c>
-      <c r="I164" t="n">
-        <v>7</v>
-      </c>
-      <c r="J164" t="n">
-        <v>3</v>
-      </c>
-      <c r="K164" t="s">
-        <v>52</v>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" t="s">
-        <v>28</v>
-      </c>
-      <c r="N164" t="s">
-        <v>29</v>
-      </c>
-      <c r="O164"/>
-      <c r="P164" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q164"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>329</v>
-      </c>
-      <c r="B165" t="b">
-        <v>1</v>
-      </c>
-      <c r="C165" t="s">
-        <v>17</v>
-      </c>
-      <c r="D165" t="s">
-        <v>18</v>
-      </c>
-      <c r="E165" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="n">
-        <v>2</v>
-      </c>
-      <c r="H165" t="s">
-        <v>35</v>
-      </c>
-      <c r="I165" t="n">
-        <v>7</v>
-      </c>
-      <c r="J165" t="n">
-        <v>3</v>
-      </c>
-      <c r="K165" t="s">
-        <v>52</v>
-      </c>
-      <c r="L165" t="n">
-        <v>2</v>
-      </c>
-      <c r="M165" t="s">
-        <v>28</v>
-      </c>
-      <c r="N165" t="s">
-        <v>29</v>
-      </c>
-      <c r="O165"/>
-      <c r="P165" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q165"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>330</v>
-      </c>
-      <c r="B166" t="b">
-        <v>1</v>
-      </c>
-      <c r="C166" t="s">
-        <v>17</v>
-      </c>
-      <c r="D166" t="s">
-        <v>18</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" t="n">
-        <v>2</v>
-      </c>
-      <c r="H166" t="s">
-        <v>35</v>
-      </c>
-      <c r="I166" t="n">
-        <v>7</v>
-      </c>
-      <c r="J166" t="n">
-        <v>3</v>
-      </c>
-      <c r="K166" t="s">
-        <v>52</v>
-      </c>
-      <c r="L166" t="n">
-        <v>3</v>
-      </c>
-      <c r="M166" t="s">
-        <v>28</v>
-      </c>
-      <c r="N166" t="s">
-        <v>29</v>
-      </c>
-      <c r="O166"/>
-      <c r="P166" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q166"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>334</v>
-      </c>
-      <c r="B167" t="b">
-        <v>0</v>
-      </c>
-      <c r="C167" t="s">
-        <v>17</v>
-      </c>
-      <c r="D167" t="s">
-        <v>18</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>2</v>
-      </c>
-      <c r="G167" t="n">
-        <v>2</v>
-      </c>
-      <c r="H167" t="s">
-        <v>36</v>
-      </c>
-      <c r="I167" t="n">
-        <v>7</v>
-      </c>
-      <c r="J167" t="n">
-        <v>3</v>
-      </c>
-      <c r="K167" t="s">
-        <v>54</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="s">
-        <v>55</v>
-      </c>
-      <c r="N167" t="s">
-        <v>32</v>
-      </c>
-      <c r="O167" t="n">
-        <v>7</v>
-      </c>
-      <c r="P167" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>335</v>
-      </c>
-      <c r="B168" t="b">
-        <v>0</v>
-      </c>
-      <c r="C168" t="s">
-        <v>17</v>
-      </c>
-      <c r="D168" t="s">
-        <v>18</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" t="n">
-        <v>2</v>
-      </c>
-      <c r="G168" t="n">
-        <v>2</v>
-      </c>
-      <c r="H168" t="s">
-        <v>36</v>
-      </c>
-      <c r="I168" t="n">
-        <v>7</v>
-      </c>
-      <c r="J168" t="n">
-        <v>3</v>
-      </c>
-      <c r="K168" t="s">
-        <v>54</v>
-      </c>
-      <c r="L168" t="n">
-        <v>2</v>
-      </c>
-      <c r="M168" t="s">
-        <v>55</v>
-      </c>
-      <c r="N168" t="s">
-        <v>32</v>
-      </c>
-      <c r="O168" t="n">
-        <v>7</v>
-      </c>
-      <c r="P168" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>336</v>
-      </c>
-      <c r="B169" t="b">
-        <v>0</v>
-      </c>
-      <c r="C169" t="s">
-        <v>17</v>
-      </c>
-      <c r="D169" t="s">
-        <v>18</v>
-      </c>
-      <c r="E169" t="n">
-        <v>2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>2</v>
-      </c>
-      <c r="G169" t="n">
-        <v>2</v>
-      </c>
-      <c r="H169" t="s">
-        <v>36</v>
-      </c>
-      <c r="I169" t="n">
-        <v>7</v>
-      </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="s">
-        <v>54</v>
-      </c>
-      <c r="L169" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" t="s">
-        <v>55</v>
-      </c>
-      <c r="N169" t="s">
-        <v>32</v>
-      </c>
-      <c r="O169" t="n">
-        <v>7</v>
-      </c>
-      <c r="P169" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>340</v>
-      </c>
-      <c r="B170" t="b">
-        <v>0</v>
-      </c>
-      <c r="C170" t="s">
-        <v>17</v>
-      </c>
-      <c r="D170" t="s">
-        <v>18</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" t="s">
-        <v>19</v>
-      </c>
-      <c r="I170" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" t="n">
-        <v>3</v>
-      </c>
-      <c r="K170" t="s">
-        <v>56</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="s">
-        <v>53</v>
-      </c>
-      <c r="N170" t="s">
-        <v>22</v>
-      </c>
-      <c r="O170" t="n">
-        <v>11</v>
-      </c>
-      <c r="P170" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>341</v>
-      </c>
-      <c r="B171" t="b">
-        <v>0</v>
-      </c>
-      <c r="C171" t="s">
-        <v>17</v>
-      </c>
-      <c r="D171" t="s">
-        <v>18</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" t="s">
-        <v>19</v>
-      </c>
-      <c r="I171" t="n">
-        <v>8</v>
-      </c>
-      <c r="J171" t="n">
-        <v>3</v>
-      </c>
-      <c r="K171" t="s">
-        <v>56</v>
-      </c>
-      <c r="L171" t="n">
-        <v>2</v>
-      </c>
-      <c r="M171" t="s">
-        <v>53</v>
-      </c>
-      <c r="N171" t="s">
-        <v>22</v>
-      </c>
-      <c r="O171" t="n">
-        <v>11</v>
-      </c>
-      <c r="P171" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>342</v>
-      </c>
-      <c r="B172" t="b">
-        <v>0</v>
-      </c>
-      <c r="C172" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" t="s">
-        <v>18</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" t="s">
-        <v>19</v>
-      </c>
-      <c r="I172" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" t="n">
-        <v>3</v>
-      </c>
-      <c r="K172" t="s">
-        <v>56</v>
-      </c>
-      <c r="L172" t="n">
-        <v>3</v>
-      </c>
-      <c r="M172" t="s">
-        <v>53</v>
-      </c>
-      <c r="N172" t="s">
-        <v>22</v>
-      </c>
-      <c r="O172" t="n">
-        <v>11</v>
-      </c>
-      <c r="P172" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>346</v>
-      </c>
-      <c r="B173" t="b">
-        <v>1</v>
-      </c>
-      <c r="C173" t="s">
-        <v>17</v>
-      </c>
-      <c r="D173" t="s">
-        <v>18</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" t="n">
-        <v>2</v>
-      </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
-      <c r="H173" t="s">
-        <v>23</v>
-      </c>
-      <c r="I173" t="n">
-        <v>8</v>
-      </c>
-      <c r="J173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K173" t="s">
-        <v>54</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
-      <c r="M173" t="s">
-        <v>25</v>
-      </c>
-      <c r="N173" t="s">
-        <v>26</v>
-      </c>
-      <c r="O173"/>
-      <c r="P173" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q173"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>347</v>
-      </c>
-      <c r="B174" t="b">
-        <v>1</v>
-      </c>
-      <c r="C174" t="s">
-        <v>17</v>
-      </c>
-      <c r="D174" t="s">
-        <v>18</v>
-      </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" t="n">
-        <v>2</v>
-      </c>
-      <c r="G174" t="n">
-        <v>1</v>
-      </c>
-      <c r="H174" t="s">
-        <v>23</v>
-      </c>
-      <c r="I174" t="n">
-        <v>8</v>
-      </c>
-      <c r="J174" t="n">
-        <v>3</v>
-      </c>
-      <c r="K174" t="s">
-        <v>54</v>
-      </c>
-      <c r="L174" t="n">
-        <v>2</v>
-      </c>
-      <c r="M174" t="s">
-        <v>25</v>
-      </c>
-      <c r="N174" t="s">
-        <v>26</v>
-      </c>
-      <c r="O174"/>
-      <c r="P174" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q174"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>348</v>
-      </c>
-      <c r="B175" t="b">
-        <v>1</v>
-      </c>
-      <c r="C175" t="s">
-        <v>17</v>
-      </c>
-      <c r="D175" t="s">
-        <v>18</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" t="n">
-        <v>2</v>
-      </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" t="s">
-        <v>23</v>
-      </c>
-      <c r="I175" t="n">
-        <v>8</v>
-      </c>
-      <c r="J175" t="n">
-        <v>3</v>
-      </c>
-      <c r="K175" t="s">
-        <v>54</v>
-      </c>
-      <c r="L175" t="n">
-        <v>3</v>
-      </c>
-      <c r="M175" t="s">
-        <v>25</v>
-      </c>
-      <c r="N175" t="s">
-        <v>26</v>
-      </c>
-      <c r="O175"/>
-      <c r="P175" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q175"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>352</v>
-      </c>
-      <c r="B176" t="b">
-        <v>1</v>
-      </c>
-      <c r="C176" t="s">
-        <v>17</v>
-      </c>
-      <c r="D176" t="s">
-        <v>18</v>
-      </c>
-      <c r="E176" t="n">
-        <v>2</v>
-      </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" t="s">
-        <v>27</v>
-      </c>
-      <c r="I176" t="n">
-        <v>8</v>
-      </c>
-      <c r="J176" t="n">
-        <v>3</v>
-      </c>
-      <c r="K176" t="s">
-        <v>56</v>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
-      </c>
-      <c r="M176" t="s">
-        <v>28</v>
-      </c>
-      <c r="N176" t="s">
-        <v>29</v>
-      </c>
-      <c r="O176"/>
-      <c r="P176" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q176"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>353</v>
-      </c>
-      <c r="B177" t="b">
-        <v>1</v>
-      </c>
-      <c r="C177" t="s">
-        <v>17</v>
-      </c>
-      <c r="D177" t="s">
-        <v>18</v>
-      </c>
-      <c r="E177" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H177" t="s">
-        <v>27</v>
-      </c>
-      <c r="I177" t="n">
-        <v>8</v>
-      </c>
-      <c r="J177" t="n">
-        <v>3</v>
-      </c>
-      <c r="K177" t="s">
-        <v>56</v>
-      </c>
-      <c r="L177" t="n">
-        <v>2</v>
-      </c>
-      <c r="M177" t="s">
-        <v>28</v>
-      </c>
-      <c r="N177" t="s">
-        <v>29</v>
-      </c>
-      <c r="O177"/>
-      <c r="P177" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q177"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>354</v>
-      </c>
-      <c r="B178" t="b">
-        <v>1</v>
-      </c>
-      <c r="C178" t="s">
-        <v>17</v>
-      </c>
-      <c r="D178" t="s">
-        <v>18</v>
-      </c>
-      <c r="E178" t="n">
-        <v>2</v>
-      </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" t="n">
-        <v>1</v>
-      </c>
-      <c r="H178" t="s">
-        <v>27</v>
-      </c>
-      <c r="I178" t="n">
-        <v>8</v>
-      </c>
-      <c r="J178" t="n">
-        <v>3</v>
-      </c>
-      <c r="K178" t="s">
-        <v>56</v>
-      </c>
-      <c r="L178" t="n">
-        <v>3</v>
-      </c>
-      <c r="M178" t="s">
-        <v>28</v>
-      </c>
-      <c r="N178" t="s">
-        <v>29</v>
-      </c>
-      <c r="O178"/>
-      <c r="P178" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q178"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>358</v>
-      </c>
-      <c r="B179" t="b">
-        <v>0</v>
-      </c>
-      <c r="C179" t="s">
-        <v>17</v>
-      </c>
-      <c r="D179" t="s">
-        <v>18</v>
-      </c>
-      <c r="E179" t="n">
-        <v>2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>2</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="s">
-        <v>30</v>
-      </c>
-      <c r="I179" t="n">
-        <v>8</v>
-      </c>
-      <c r="J179" t="n">
-        <v>3</v>
-      </c>
-      <c r="K179" t="s">
-        <v>54</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="s">
-        <v>55</v>
-      </c>
-      <c r="N179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O179" t="n">
-        <v>7</v>
-      </c>
-      <c r="P179" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>359</v>
-      </c>
-      <c r="B180" t="b">
-        <v>0</v>
-      </c>
-      <c r="C180" t="s">
-        <v>17</v>
-      </c>
-      <c r="D180" t="s">
-        <v>18</v>
-      </c>
-      <c r="E180" t="n">
-        <v>2</v>
-      </c>
-      <c r="F180" t="n">
-        <v>2</v>
-      </c>
-      <c r="G180" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" t="s">
-        <v>30</v>
-      </c>
-      <c r="I180" t="n">
-        <v>8</v>
-      </c>
-      <c r="J180" t="n">
-        <v>3</v>
-      </c>
-      <c r="K180" t="s">
-        <v>54</v>
-      </c>
-      <c r="L180" t="n">
-        <v>2</v>
-      </c>
-      <c r="M180" t="s">
-        <v>55</v>
-      </c>
-      <c r="N180" t="s">
-        <v>32</v>
-      </c>
-      <c r="O180" t="n">
-        <v>7</v>
-      </c>
-      <c r="P180" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>360</v>
-      </c>
-      <c r="B181" t="b">
-        <v>0</v>
-      </c>
-      <c r="C181" t="s">
-        <v>17</v>
-      </c>
-      <c r="D181" t="s">
-        <v>18</v>
-      </c>
-      <c r="E181" t="n">
-        <v>2</v>
-      </c>
-      <c r="F181" t="n">
-        <v>2</v>
-      </c>
-      <c r="G181" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" t="s">
-        <v>30</v>
-      </c>
-      <c r="I181" t="n">
-        <v>8</v>
-      </c>
-      <c r="J181" t="n">
-        <v>3</v>
-      </c>
-      <c r="K181" t="s">
-        <v>54</v>
-      </c>
-      <c r="L181" t="n">
-        <v>3</v>
-      </c>
-      <c r="M181" t="s">
-        <v>55</v>
-      </c>
-      <c r="N181" t="s">
-        <v>32</v>
-      </c>
-      <c r="O181" t="n">
-        <v>7</v>
-      </c>
-      <c r="P181" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>364</v>
-      </c>
-      <c r="B182" t="b">
-        <v>0</v>
-      </c>
-      <c r="C182" t="s">
-        <v>17</v>
-      </c>
-      <c r="D182" t="s">
-        <v>18</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" t="n">
-        <v>2</v>
-      </c>
-      <c r="H182" t="s">
-        <v>33</v>
-      </c>
-      <c r="I182" t="n">
-        <v>8</v>
-      </c>
-      <c r="J182" t="n">
-        <v>3</v>
-      </c>
-      <c r="K182" t="s">
-        <v>56</v>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="s">
-        <v>53</v>
-      </c>
-      <c r="N182" t="s">
-        <v>22</v>
-      </c>
-      <c r="O182" t="n">
-        <v>11</v>
-      </c>
-      <c r="P182" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>365</v>
-      </c>
-      <c r="B183" t="b">
-        <v>0</v>
-      </c>
-      <c r="C183" t="s">
-        <v>17</v>
-      </c>
-      <c r="D183" t="s">
-        <v>18</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="n">
-        <v>2</v>
-      </c>
-      <c r="H183" t="s">
-        <v>33</v>
-      </c>
-      <c r="I183" t="n">
-        <v>8</v>
-      </c>
-      <c r="J183" t="n">
-        <v>3</v>
-      </c>
-      <c r="K183" t="s">
-        <v>56</v>
-      </c>
-      <c r="L183" t="n">
-        <v>2</v>
-      </c>
-      <c r="M183" t="s">
-        <v>53</v>
-      </c>
-      <c r="N183" t="s">
-        <v>22</v>
-      </c>
-      <c r="O183" t="n">
-        <v>11</v>
-      </c>
-      <c r="P183" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>366</v>
-      </c>
-      <c r="B184" t="b">
-        <v>0</v>
-      </c>
-      <c r="C184" t="s">
-        <v>17</v>
-      </c>
-      <c r="D184" t="s">
-        <v>18</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" t="n">
-        <v>2</v>
-      </c>
-      <c r="H184" t="s">
-        <v>33</v>
-      </c>
-      <c r="I184" t="n">
-        <v>8</v>
-      </c>
-      <c r="J184" t="n">
-        <v>3</v>
-      </c>
-      <c r="K184" t="s">
-        <v>56</v>
-      </c>
-      <c r="L184" t="n">
-        <v>3</v>
-      </c>
-      <c r="M184" t="s">
-        <v>53</v>
-      </c>
-      <c r="N184" t="s">
-        <v>22</v>
-      </c>
-      <c r="O184" t="n">
-        <v>11</v>
-      </c>
-      <c r="P184" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>370</v>
-      </c>
-      <c r="B185" t="b">
-        <v>1</v>
-      </c>
-      <c r="C185" t="s">
-        <v>17</v>
-      </c>
-      <c r="D185" t="s">
-        <v>18</v>
-      </c>
-      <c r="E185" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" t="n">
-        <v>2</v>
-      </c>
-      <c r="G185" t="n">
-        <v>2</v>
-      </c>
-      <c r="H185" t="s">
-        <v>34</v>
-      </c>
-      <c r="I185" t="n">
-        <v>8</v>
-      </c>
-      <c r="J185" t="n">
-        <v>3</v>
-      </c>
-      <c r="K185" t="s">
-        <v>54</v>
-      </c>
-      <c r="L185" t="n">
-        <v>1</v>
-      </c>
-      <c r="M185" t="s">
-        <v>25</v>
-      </c>
-      <c r="N185" t="s">
-        <v>26</v>
-      </c>
-      <c r="O185"/>
-      <c r="P185" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q185"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>371</v>
-      </c>
-      <c r="B186" t="b">
-        <v>1</v>
-      </c>
-      <c r="C186" t="s">
-        <v>17</v>
-      </c>
-      <c r="D186" t="s">
-        <v>18</v>
-      </c>
-      <c r="E186" t="n">
-        <v>1</v>
-      </c>
-      <c r="F186" t="n">
-        <v>2</v>
-      </c>
-      <c r="G186" t="n">
-        <v>2</v>
-      </c>
-      <c r="H186" t="s">
-        <v>34</v>
-      </c>
-      <c r="I186" t="n">
-        <v>8</v>
-      </c>
-      <c r="J186" t="n">
-        <v>3</v>
-      </c>
-      <c r="K186" t="s">
-        <v>54</v>
-      </c>
-      <c r="L186" t="n">
-        <v>2</v>
-      </c>
-      <c r="M186" t="s">
-        <v>25</v>
-      </c>
-      <c r="N186" t="s">
-        <v>26</v>
-      </c>
-      <c r="O186"/>
-      <c r="P186" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q186"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>372</v>
-      </c>
-      <c r="B187" t="b">
-        <v>1</v>
-      </c>
-      <c r="C187" t="s">
-        <v>17</v>
-      </c>
-      <c r="D187" t="s">
-        <v>18</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" t="n">
-        <v>2</v>
-      </c>
-      <c r="G187" t="n">
-        <v>2</v>
-      </c>
-      <c r="H187" t="s">
-        <v>34</v>
-      </c>
-      <c r="I187" t="n">
-        <v>8</v>
-      </c>
-      <c r="J187" t="n">
-        <v>3</v>
-      </c>
-      <c r="K187" t="s">
-        <v>54</v>
-      </c>
-      <c r="L187" t="n">
-        <v>3</v>
-      </c>
-      <c r="M187" t="s">
-        <v>25</v>
-      </c>
-      <c r="N187" t="s">
-        <v>26</v>
-      </c>
-      <c r="O187"/>
-      <c r="P187" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q187"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>376</v>
-      </c>
-      <c r="B188" t="b">
-        <v>1</v>
-      </c>
-      <c r="C188" t="s">
-        <v>17</v>
-      </c>
-      <c r="D188" t="s">
-        <v>18</v>
-      </c>
-      <c r="E188" t="n">
-        <v>2</v>
-      </c>
-      <c r="F188" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" t="n">
-        <v>2</v>
-      </c>
-      <c r="H188" t="s">
-        <v>35</v>
-      </c>
-      <c r="I188" t="n">
-        <v>8</v>
-      </c>
-      <c r="J188" t="n">
-        <v>3</v>
-      </c>
-      <c r="K188" t="s">
-        <v>56</v>
-      </c>
-      <c r="L188" t="n">
-        <v>1</v>
-      </c>
-      <c r="M188" t="s">
-        <v>28</v>
-      </c>
-      <c r="N188" t="s">
-        <v>29</v>
-      </c>
-      <c r="O188"/>
-      <c r="P188" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q188"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>377</v>
-      </c>
-      <c r="B189" t="b">
-        <v>1</v>
-      </c>
-      <c r="C189" t="s">
-        <v>17</v>
-      </c>
-      <c r="D189" t="s">
-        <v>18</v>
-      </c>
-      <c r="E189" t="n">
-        <v>2</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" t="n">
-        <v>2</v>
-      </c>
-      <c r="H189" t="s">
-        <v>35</v>
-      </c>
-      <c r="I189" t="n">
-        <v>8</v>
-      </c>
-      <c r="J189" t="n">
-        <v>3</v>
-      </c>
-      <c r="K189" t="s">
-        <v>56</v>
-      </c>
-      <c r="L189" t="n">
-        <v>2</v>
-      </c>
-      <c r="M189" t="s">
-        <v>28</v>
-      </c>
-      <c r="N189" t="s">
-        <v>29</v>
-      </c>
-      <c r="O189"/>
-      <c r="P189" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q189"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>378</v>
-      </c>
-      <c r="B190" t="b">
-        <v>1</v>
-      </c>
-      <c r="C190" t="s">
-        <v>17</v>
-      </c>
-      <c r="D190" t="s">
-        <v>18</v>
-      </c>
-      <c r="E190" t="n">
-        <v>2</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" t="n">
-        <v>2</v>
-      </c>
-      <c r="H190" t="s">
-        <v>35</v>
-      </c>
-      <c r="I190" t="n">
-        <v>8</v>
-      </c>
-      <c r="J190" t="n">
-        <v>3</v>
-      </c>
-      <c r="K190" t="s">
-        <v>56</v>
-      </c>
-      <c r="L190" t="n">
-        <v>3</v>
-      </c>
-      <c r="M190" t="s">
-        <v>28</v>
-      </c>
-      <c r="N190" t="s">
-        <v>29</v>
-      </c>
-      <c r="O190"/>
-      <c r="P190" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q190"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>382</v>
-      </c>
-      <c r="B191" t="b">
-        <v>0</v>
-      </c>
-      <c r="C191" t="s">
-        <v>17</v>
-      </c>
-      <c r="D191" t="s">
-        <v>18</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" t="n">
-        <v>2</v>
-      </c>
-      <c r="H191" t="s">
-        <v>36</v>
-      </c>
-      <c r="I191" t="n">
-        <v>8</v>
-      </c>
-      <c r="J191" t="n">
-        <v>3</v>
-      </c>
-      <c r="K191" t="s">
-        <v>54</v>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="s">
-        <v>55</v>
-      </c>
-      <c r="N191" t="s">
-        <v>32</v>
-      </c>
-      <c r="O191" t="n">
-        <v>7</v>
-      </c>
-      <c r="P191" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>383</v>
-      </c>
-      <c r="B192" t="b">
-        <v>0</v>
-      </c>
-      <c r="C192" t="s">
-        <v>17</v>
-      </c>
-      <c r="D192" t="s">
-        <v>18</v>
-      </c>
-      <c r="E192" t="n">
-        <v>2</v>
-      </c>
-      <c r="F192" t="n">
-        <v>2</v>
-      </c>
-      <c r="G192" t="n">
-        <v>2</v>
-      </c>
-      <c r="H192" t="s">
-        <v>36</v>
-      </c>
-      <c r="I192" t="n">
-        <v>8</v>
-      </c>
-      <c r="J192" t="n">
-        <v>3</v>
-      </c>
-      <c r="K192" t="s">
-        <v>54</v>
-      </c>
-      <c r="L192" t="n">
-        <v>2</v>
-      </c>
-      <c r="M192" t="s">
-        <v>55</v>
-      </c>
-      <c r="N192" t="s">
-        <v>32</v>
-      </c>
-      <c r="O192" t="n">
-        <v>7</v>
-      </c>
-      <c r="P192" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>384</v>
-      </c>
-      <c r="B193" t="b">
-        <v>0</v>
-      </c>
-      <c r="C193" t="s">
-        <v>17</v>
-      </c>
-      <c r="D193" t="s">
-        <v>18</v>
-      </c>
-      <c r="E193" t="n">
-        <v>2</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="n">
-        <v>2</v>
-      </c>
-      <c r="H193" t="s">
-        <v>36</v>
-      </c>
-      <c r="I193" t="n">
-        <v>8</v>
-      </c>
-      <c r="J193" t="n">
-        <v>3</v>
-      </c>
-      <c r="K193" t="s">
-        <v>54</v>
-      </c>
-      <c r="L193" t="n">
-        <v>3</v>
-      </c>
-      <c r="M193" t="s">
-        <v>55</v>
-      </c>
-      <c r="N193" t="s">
-        <v>32</v>
-      </c>
-      <c r="O193" t="n">
-        <v>7</v>
-      </c>
-      <c r="P193" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>388</v>
-      </c>
-      <c r="B194" t="b">
-        <v>0</v>
-      </c>
-      <c r="C194" t="s">
-        <v>17</v>
-      </c>
-      <c r="D194" t="s">
-        <v>18</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" t="n">
-        <v>1</v>
-      </c>
-      <c r="H194" t="s">
-        <v>19</v>
-      </c>
-      <c r="I194" t="n">
-        <v>9</v>
-      </c>
-      <c r="J194" t="n">
-        <v>3</v>
-      </c>
-      <c r="K194" t="s">
-        <v>57</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
-      <c r="M194" t="s">
-        <v>58</v>
-      </c>
-      <c r="N194" t="s">
-        <v>22</v>
-      </c>
-      <c r="O194" t="n">
-        <v>8</v>
-      </c>
-      <c r="P194" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>389</v>
-      </c>
-      <c r="B195" t="b">
-        <v>0</v>
-      </c>
-      <c r="C195" t="s">
-        <v>17</v>
-      </c>
-      <c r="D195" t="s">
-        <v>18</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" t="n">
-        <v>1</v>
-      </c>
-      <c r="H195" t="s">
-        <v>19</v>
-      </c>
-      <c r="I195" t="n">
-        <v>9</v>
-      </c>
-      <c r="J195" t="n">
-        <v>3</v>
-      </c>
-      <c r="K195" t="s">
-        <v>57</v>
-      </c>
-      <c r="L195" t="n">
-        <v>2</v>
-      </c>
-      <c r="M195" t="s">
-        <v>58</v>
-      </c>
-      <c r="N195" t="s">
-        <v>22</v>
-      </c>
-      <c r="O195" t="n">
-        <v>8</v>
-      </c>
-      <c r="P195" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>390</v>
-      </c>
-      <c r="B196" t="b">
-        <v>0</v>
-      </c>
-      <c r="C196" t="s">
-        <v>17</v>
-      </c>
-      <c r="D196" t="s">
-        <v>18</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" t="s">
-        <v>19</v>
-      </c>
-      <c r="I196" t="n">
-        <v>9</v>
-      </c>
-      <c r="J196" t="n">
-        <v>3</v>
-      </c>
-      <c r="K196" t="s">
-        <v>57</v>
-      </c>
-      <c r="L196" t="n">
-        <v>3</v>
-      </c>
-      <c r="M196" t="s">
-        <v>58</v>
-      </c>
-      <c r="N196" t="s">
-        <v>22</v>
-      </c>
-      <c r="O196" t="n">
-        <v>8</v>
-      </c>
-      <c r="P196" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>394</v>
-      </c>
-      <c r="B197" t="b">
-        <v>1</v>
-      </c>
-      <c r="C197" t="s">
-        <v>17</v>
-      </c>
-      <c r="D197" t="s">
-        <v>18</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="s">
-        <v>23</v>
-      </c>
-      <c r="I197" t="n">
-        <v>9</v>
-      </c>
-      <c r="J197" t="n">
-        <v>3</v>
-      </c>
-      <c r="K197" t="s">
-        <v>54</v>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
-      </c>
-      <c r="M197" t="s">
-        <v>25</v>
-      </c>
-      <c r="N197" t="s">
-        <v>26</v>
-      </c>
-      <c r="O197"/>
-      <c r="P197" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q197"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>395</v>
-      </c>
-      <c r="B198" t="b">
-        <v>1</v>
-      </c>
-      <c r="C198" t="s">
-        <v>17</v>
-      </c>
-      <c r="D198" t="s">
-        <v>18</v>
-      </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" t="s">
-        <v>23</v>
-      </c>
-      <c r="I198" t="n">
-        <v>9</v>
-      </c>
-      <c r="J198" t="n">
-        <v>3</v>
-      </c>
-      <c r="K198" t="s">
-        <v>54</v>
-      </c>
-      <c r="L198" t="n">
-        <v>2</v>
-      </c>
-      <c r="M198" t="s">
-        <v>25</v>
-      </c>
-      <c r="N198" t="s">
-        <v>26</v>
-      </c>
-      <c r="O198"/>
-      <c r="P198" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q198"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>396</v>
-      </c>
-      <c r="B199" t="b">
-        <v>1</v>
-      </c>
-      <c r="C199" t="s">
-        <v>17</v>
-      </c>
-      <c r="D199" t="s">
-        <v>18</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1</v>
-      </c>
-      <c r="H199" t="s">
-        <v>23</v>
-      </c>
-      <c r="I199" t="n">
-        <v>9</v>
-      </c>
-      <c r="J199" t="n">
-        <v>3</v>
-      </c>
-      <c r="K199" t="s">
-        <v>54</v>
-      </c>
-      <c r="L199" t="n">
-        <v>3</v>
-      </c>
-      <c r="M199" t="s">
-        <v>25</v>
-      </c>
-      <c r="N199" t="s">
-        <v>26</v>
-      </c>
-      <c r="O199"/>
-      <c r="P199" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q199"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>400</v>
-      </c>
-      <c r="B200" t="b">
-        <v>1</v>
-      </c>
-      <c r="C200" t="s">
-        <v>17</v>
-      </c>
-      <c r="D200" t="s">
-        <v>18</v>
-      </c>
-      <c r="E200" t="n">
-        <v>2</v>
-      </c>
-      <c r="F200" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" t="n">
-        <v>1</v>
-      </c>
-      <c r="H200" t="s">
-        <v>27</v>
-      </c>
-      <c r="I200" t="n">
-        <v>9</v>
-      </c>
-      <c r="J200" t="n">
-        <v>3</v>
-      </c>
-      <c r="K200" t="s">
-        <v>57</v>
-      </c>
-      <c r="L200" t="n">
-        <v>1</v>
-      </c>
-      <c r="M200" t="s">
-        <v>28</v>
-      </c>
-      <c r="N200" t="s">
-        <v>29</v>
-      </c>
-      <c r="O200"/>
-      <c r="P200" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q200"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>401</v>
-      </c>
-      <c r="B201" t="b">
-        <v>1</v>
-      </c>
-      <c r="C201" t="s">
-        <v>17</v>
-      </c>
-      <c r="D201" t="s">
-        <v>18</v>
-      </c>
-      <c r="E201" t="n">
-        <v>2</v>
-      </c>
-      <c r="F201" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" t="s">
-        <v>27</v>
-      </c>
-      <c r="I201" t="n">
-        <v>9</v>
-      </c>
-      <c r="J201" t="n">
-        <v>3</v>
-      </c>
-      <c r="K201" t="s">
-        <v>57</v>
-      </c>
-      <c r="L201" t="n">
-        <v>2</v>
-      </c>
-      <c r="M201" t="s">
-        <v>28</v>
-      </c>
-      <c r="N201" t="s">
-        <v>29</v>
-      </c>
-      <c r="O201"/>
-      <c r="P201" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q201"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>402</v>
-      </c>
-      <c r="B202" t="b">
-        <v>1</v>
-      </c>
-      <c r="C202" t="s">
-        <v>17</v>
-      </c>
-      <c r="D202" t="s">
-        <v>18</v>
-      </c>
-      <c r="E202" t="n">
-        <v>2</v>
-      </c>
-      <c r="F202" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" t="n">
-        <v>1</v>
-      </c>
-      <c r="H202" t="s">
-        <v>27</v>
-      </c>
-      <c r="I202" t="n">
-        <v>9</v>
-      </c>
-      <c r="J202" t="n">
-        <v>3</v>
-      </c>
-      <c r="K202" t="s">
-        <v>57</v>
-      </c>
-      <c r="L202" t="n">
-        <v>3</v>
-      </c>
-      <c r="M202" t="s">
-        <v>28</v>
-      </c>
-      <c r="N202" t="s">
-        <v>29</v>
-      </c>
-      <c r="O202"/>
-      <c r="P202" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q202"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>406</v>
-      </c>
-      <c r="B203" t="b">
-        <v>0</v>
-      </c>
-      <c r="C203" t="s">
-        <v>17</v>
-      </c>
-      <c r="D203" t="s">
-        <v>18</v>
-      </c>
-      <c r="E203" t="n">
-        <v>2</v>
-      </c>
-      <c r="F203" t="n">
-        <v>2</v>
-      </c>
-      <c r="G203" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" t="s">
-        <v>30</v>
-      </c>
-      <c r="I203" t="n">
-        <v>9</v>
-      </c>
-      <c r="J203" t="n">
-        <v>3</v>
-      </c>
-      <c r="K203" t="s">
-        <v>54</v>
-      </c>
-      <c r="L203" t="n">
-        <v>1</v>
-      </c>
-      <c r="M203" t="s">
-        <v>55</v>
-      </c>
-      <c r="N203" t="s">
-        <v>32</v>
-      </c>
-      <c r="O203" t="n">
-        <v>7</v>
-      </c>
-      <c r="P203" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>407</v>
-      </c>
-      <c r="B204" t="b">
-        <v>0</v>
-      </c>
-      <c r="C204" t="s">
-        <v>17</v>
-      </c>
-      <c r="D204" t="s">
-        <v>18</v>
-      </c>
-      <c r="E204" t="n">
-        <v>2</v>
-      </c>
-      <c r="F204" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="s">
-        <v>30</v>
-      </c>
-      <c r="I204" t="n">
-        <v>9</v>
-      </c>
-      <c r="J204" t="n">
-        <v>3</v>
-      </c>
-      <c r="K204" t="s">
-        <v>54</v>
-      </c>
-      <c r="L204" t="n">
-        <v>2</v>
-      </c>
-      <c r="M204" t="s">
-        <v>55</v>
-      </c>
-      <c r="N204" t="s">
-        <v>32</v>
-      </c>
-      <c r="O204" t="n">
-        <v>7</v>
-      </c>
-      <c r="P204" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>408</v>
-      </c>
-      <c r="B205" t="b">
-        <v>0</v>
-      </c>
-      <c r="C205" t="s">
-        <v>17</v>
-      </c>
-      <c r="D205" t="s">
-        <v>18</v>
-      </c>
-      <c r="E205" t="n">
-        <v>2</v>
-      </c>
-      <c r="F205" t="n">
-        <v>2</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1</v>
-      </c>
-      <c r="H205" t="s">
-        <v>30</v>
-      </c>
-      <c r="I205" t="n">
-        <v>9</v>
-      </c>
-      <c r="J205" t="n">
-        <v>3</v>
-      </c>
-      <c r="K205" t="s">
-        <v>54</v>
-      </c>
-      <c r="L205" t="n">
-        <v>3</v>
-      </c>
-      <c r="M205" t="s">
-        <v>55</v>
-      </c>
-      <c r="N205" t="s">
-        <v>32</v>
-      </c>
-      <c r="O205" t="n">
-        <v>7</v>
-      </c>
-      <c r="P205" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q205" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>412</v>
-      </c>
-      <c r="B206" t="b">
-        <v>0</v>
-      </c>
-      <c r="C206" t="s">
-        <v>17</v>
-      </c>
-      <c r="D206" t="s">
-        <v>18</v>
-      </c>
-      <c r="E206" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" t="n">
-        <v>2</v>
-      </c>
-      <c r="H206" t="s">
-        <v>33</v>
-      </c>
-      <c r="I206" t="n">
-        <v>9</v>
-      </c>
-      <c r="J206" t="n">
-        <v>3</v>
-      </c>
-      <c r="K206" t="s">
-        <v>57</v>
-      </c>
-      <c r="L206" t="n">
-        <v>1</v>
-      </c>
-      <c r="M206" t="s">
-        <v>58</v>
-      </c>
-      <c r="N206" t="s">
-        <v>22</v>
-      </c>
-      <c r="O206" t="n">
-        <v>8</v>
-      </c>
-      <c r="P206" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>413</v>
-      </c>
-      <c r="B207" t="b">
-        <v>0</v>
-      </c>
-      <c r="C207" t="s">
-        <v>17</v>
-      </c>
-      <c r="D207" t="s">
-        <v>18</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" t="n">
-        <v>2</v>
-      </c>
-      <c r="H207" t="s">
-        <v>33</v>
-      </c>
-      <c r="I207" t="n">
-        <v>9</v>
-      </c>
-      <c r="J207" t="n">
-        <v>3</v>
-      </c>
-      <c r="K207" t="s">
-        <v>57</v>
-      </c>
-      <c r="L207" t="n">
-        <v>2</v>
-      </c>
-      <c r="M207" t="s">
-        <v>58</v>
-      </c>
-      <c r="N207" t="s">
-        <v>22</v>
-      </c>
-      <c r="O207" t="n">
-        <v>8</v>
-      </c>
-      <c r="P207" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>414</v>
-      </c>
-      <c r="B208" t="b">
-        <v>0</v>
-      </c>
-      <c r="C208" t="s">
-        <v>17</v>
-      </c>
-      <c r="D208" t="s">
-        <v>18</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="n">
-        <v>2</v>
-      </c>
-      <c r="H208" t="s">
-        <v>33</v>
-      </c>
-      <c r="I208" t="n">
-        <v>9</v>
-      </c>
-      <c r="J208" t="n">
-        <v>3</v>
-      </c>
-      <c r="K208" t="s">
-        <v>57</v>
-      </c>
-      <c r="L208" t="n">
-        <v>3</v>
-      </c>
-      <c r="M208" t="s">
-        <v>58</v>
-      </c>
-      <c r="N208" t="s">
-        <v>22</v>
-      </c>
-      <c r="O208" t="n">
-        <v>8</v>
-      </c>
-      <c r="P208" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>418</v>
-      </c>
-      <c r="B209" t="b">
-        <v>1</v>
-      </c>
-      <c r="C209" t="s">
-        <v>17</v>
-      </c>
-      <c r="D209" t="s">
-        <v>18</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" t="n">
-        <v>2</v>
-      </c>
-      <c r="G209" t="n">
-        <v>2</v>
-      </c>
-      <c r="H209" t="s">
-        <v>34</v>
-      </c>
-      <c r="I209" t="n">
-        <v>9</v>
-      </c>
-      <c r="J209" t="n">
-        <v>3</v>
-      </c>
-      <c r="K209" t="s">
-        <v>54</v>
-      </c>
-      <c r="L209" t="n">
-        <v>1</v>
-      </c>
-      <c r="M209" t="s">
-        <v>25</v>
-      </c>
-      <c r="N209" t="s">
-        <v>26</v>
-      </c>
-      <c r="O209"/>
-      <c r="P209" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q209"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>419</v>
-      </c>
-      <c r="B210" t="b">
-        <v>1</v>
-      </c>
-      <c r="C210" t="s">
-        <v>17</v>
-      </c>
-      <c r="D210" t="s">
-        <v>18</v>
-      </c>
-      <c r="E210" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G210" t="n">
-        <v>2</v>
-      </c>
-      <c r="H210" t="s">
-        <v>34</v>
-      </c>
-      <c r="I210" t="n">
-        <v>9</v>
-      </c>
-      <c r="J210" t="n">
-        <v>3</v>
-      </c>
-      <c r="K210" t="s">
-        <v>54</v>
-      </c>
-      <c r="L210" t="n">
-        <v>2</v>
-      </c>
-      <c r="M210" t="s">
-        <v>25</v>
-      </c>
-      <c r="N210" t="s">
-        <v>26</v>
-      </c>
-      <c r="O210"/>
-      <c r="P210" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q210"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>420</v>
-      </c>
-      <c r="B211" t="b">
-        <v>1</v>
-      </c>
-      <c r="C211" t="s">
-        <v>17</v>
-      </c>
-      <c r="D211" t="s">
-        <v>18</v>
-      </c>
-      <c r="E211" t="n">
-        <v>1</v>
-      </c>
-      <c r="F211" t="n">
-        <v>2</v>
-      </c>
-      <c r="G211" t="n">
-        <v>2</v>
-      </c>
-      <c r="H211" t="s">
-        <v>34</v>
-      </c>
-      <c r="I211" t="n">
-        <v>9</v>
-      </c>
-      <c r="J211" t="n">
-        <v>3</v>
-      </c>
-      <c r="K211" t="s">
-        <v>54</v>
-      </c>
-      <c r="L211" t="n">
-        <v>3</v>
-      </c>
-      <c r="M211" t="s">
-        <v>25</v>
-      </c>
-      <c r="N211" t="s">
-        <v>26</v>
-      </c>
-      <c r="O211"/>
-      <c r="P211" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q211"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>424</v>
-      </c>
-      <c r="B212" t="b">
-        <v>1</v>
-      </c>
-      <c r="C212" t="s">
-        <v>17</v>
-      </c>
-      <c r="D212" t="s">
-        <v>18</v>
-      </c>
-      <c r="E212" t="n">
-        <v>2</v>
-      </c>
-      <c r="F212" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" t="n">
-        <v>2</v>
-      </c>
-      <c r="H212" t="s">
-        <v>35</v>
-      </c>
-      <c r="I212" t="n">
-        <v>9</v>
-      </c>
-      <c r="J212" t="n">
-        <v>3</v>
-      </c>
-      <c r="K212" t="s">
-        <v>57</v>
-      </c>
-      <c r="L212" t="n">
-        <v>1</v>
-      </c>
-      <c r="M212" t="s">
-        <v>28</v>
-      </c>
-      <c r="N212" t="s">
-        <v>29</v>
-      </c>
-      <c r="O212"/>
-      <c r="P212" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q212"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>425</v>
-      </c>
-      <c r="B213" t="b">
-        <v>1</v>
-      </c>
-      <c r="C213" t="s">
-        <v>17</v>
-      </c>
-      <c r="D213" t="s">
-        <v>18</v>
-      </c>
-      <c r="E213" t="n">
-        <v>2</v>
-      </c>
-      <c r="F213" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" t="n">
-        <v>2</v>
-      </c>
-      <c r="H213" t="s">
-        <v>35</v>
-      </c>
-      <c r="I213" t="n">
-        <v>9</v>
-      </c>
-      <c r="J213" t="n">
-        <v>3</v>
-      </c>
-      <c r="K213" t="s">
-        <v>57</v>
-      </c>
-      <c r="L213" t="n">
-        <v>2</v>
-      </c>
-      <c r="M213" t="s">
-        <v>28</v>
-      </c>
-      <c r="N213" t="s">
-        <v>29</v>
-      </c>
-      <c r="O213"/>
-      <c r="P213" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q213"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>426</v>
-      </c>
-      <c r="B214" t="b">
-        <v>1</v>
-      </c>
-      <c r="C214" t="s">
-        <v>17</v>
-      </c>
-      <c r="D214" t="s">
-        <v>18</v>
-      </c>
-      <c r="E214" t="n">
-        <v>2</v>
-      </c>
-      <c r="F214" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" t="n">
-        <v>2</v>
-      </c>
-      <c r="H214" t="s">
-        <v>35</v>
-      </c>
-      <c r="I214" t="n">
-        <v>9</v>
-      </c>
-      <c r="J214" t="n">
-        <v>3</v>
-      </c>
-      <c r="K214" t="s">
-        <v>57</v>
-      </c>
-      <c r="L214" t="n">
-        <v>3</v>
-      </c>
-      <c r="M214" t="s">
-        <v>28</v>
-      </c>
-      <c r="N214" t="s">
-        <v>29</v>
-      </c>
-      <c r="O214"/>
-      <c r="P214" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q214"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>430</v>
-      </c>
-      <c r="B215" t="b">
-        <v>0</v>
-      </c>
-      <c r="C215" t="s">
-        <v>17</v>
-      </c>
-      <c r="D215" t="s">
-        <v>18</v>
-      </c>
-      <c r="E215" t="n">
-        <v>2</v>
-      </c>
-      <c r="F215" t="n">
-        <v>2</v>
-      </c>
-      <c r="G215" t="n">
-        <v>2</v>
-      </c>
-      <c r="H215" t="s">
-        <v>36</v>
-      </c>
-      <c r="I215" t="n">
-        <v>9</v>
-      </c>
-      <c r="J215" t="n">
-        <v>3</v>
-      </c>
-      <c r="K215" t="s">
-        <v>54</v>
-      </c>
-      <c r="L215" t="n">
-        <v>1</v>
-      </c>
-      <c r="M215" t="s">
-        <v>55</v>
-      </c>
-      <c r="N215" t="s">
-        <v>32</v>
-      </c>
-      <c r="O215" t="n">
-        <v>7</v>
-      </c>
-      <c r="P215" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>431</v>
-      </c>
-      <c r="B216" t="b">
-        <v>0</v>
-      </c>
-      <c r="C216" t="s">
-        <v>17</v>
-      </c>
-      <c r="D216" t="s">
-        <v>18</v>
-      </c>
-      <c r="E216" t="n">
-        <v>2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>2</v>
-      </c>
-      <c r="G216" t="n">
-        <v>2</v>
-      </c>
-      <c r="H216" t="s">
-        <v>36</v>
-      </c>
-      <c r="I216" t="n">
-        <v>9</v>
-      </c>
-      <c r="J216" t="n">
-        <v>3</v>
-      </c>
-      <c r="K216" t="s">
-        <v>54</v>
-      </c>
-      <c r="L216" t="n">
-        <v>2</v>
-      </c>
-      <c r="M216" t="s">
-        <v>55</v>
-      </c>
-      <c r="N216" t="s">
-        <v>32</v>
-      </c>
-      <c r="O216" t="n">
-        <v>7</v>
-      </c>
-      <c r="P216" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>432</v>
-      </c>
-      <c r="B217" t="b">
-        <v>0</v>
-      </c>
-      <c r="C217" t="s">
-        <v>17</v>
-      </c>
-      <c r="D217" t="s">
-        <v>18</v>
-      </c>
-      <c r="E217" t="n">
-        <v>2</v>
-      </c>
-      <c r="F217" t="n">
-        <v>2</v>
-      </c>
-      <c r="G217" t="n">
-        <v>2</v>
-      </c>
-      <c r="H217" t="s">
-        <v>36</v>
-      </c>
-      <c r="I217" t="n">
-        <v>9</v>
-      </c>
-      <c r="J217" t="n">
-        <v>3</v>
-      </c>
-      <c r="K217" t="s">
-        <v>54</v>
-      </c>
-      <c r="L217" t="n">
-        <v>3</v>
-      </c>
-      <c r="M217" t="s">
-        <v>55</v>
-      </c>
-      <c r="N217" t="s">
-        <v>32</v>
-      </c>
-      <c r="O217" t="n">
-        <v>7</v>
-      </c>
-      <c r="P217" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -74,44 +74,44 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2056, 2058, 2177, 2179, 2227, 2229, 2231, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(20, 21, 22, 23, 148, 149, 150, 151, 152, 1652, 1653, 1654, 1655, 1690, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2055, 2056, 2058, 2176, 2177, 2178, 2179, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e5", "e6", "e9", "e38", "e366", "e376", "e389", "e394", "e406", "e430", "e461", "e484", "e497", "e510", "e512", "e513")</t>
+    <t xml:space="preserve">c("e6", "e38", "e366", "e376", "e389", "e406", "e430", "e461", "e484", "e510", "e512", "e513")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2029, 2033, 2035, 2037, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+    <t xml:space="preserve">c(222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1728, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 1965, 2027, 2029, 2031, 2033, 2035, 2037, 2119, 2120, 2121, 2123, 2124, 2125, 2126, 2127)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e10", "e55", "e67", "e382", "e384", "e395", "e422", "e455", "e473", "e496")</t>
+    <t xml:space="preserve">c("e55", "e67", "e382", "e384", "e395", "e422", "e443", "e455", "e473")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 212, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899, 2230, 2232)</t>
+    <t xml:space="preserve">c(201, 202, 203, 204, 205, 206, 207, 208, 209, 210, 211, 213, 214, 215, 216, 217, 218, 219, 220, 265, 266, 267, 268, 1899)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e52", "e53", "e54", "e66", "e430", "e497")</t>
+    <t xml:space="preserve">c("e52", "e53", "e54", "e66", "e430")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 2026, 2028, 2030, 2032, 2034, 2036, 2108, 2109, 
-2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(13, 14, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 176, 177, 178, 179, 180, 181, 182, 223, 225, 227, 243, 244, 245, 246, 247, 248, 249, 250, 269, 270, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1812, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1874, 1875, 1876, 1935, 1990, 1991, 1992, 1993, 2026, 2028, 2030, 2032, 2034, 2036, 2107, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 
+2135, 2136, 2194, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e4", "e18", "e33", "e36", "e47", "e55", "e56", "e57", "e60", "e61", "e67", "e68", "e69", "e381", "e391", "e392", "e410", "e415", "e420", "e421", "e423", "e439", "e448", "e455", "e470", "e473", "e474", "e488", "e496", "e504", "e515", "e517")</t>
+    <t xml:space="preserve">c("e4", "e18", "e33", "e36", "e47", "e55", "e60", "e61", "e67", "e68", "e69", "e391", "e392", "e403", "e410", "e415", "e420", "e423", "e439", "e448", "e455", "e470", "e473", "e488", "e504", "e515", "e517")</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
@@ -126,51 +126,70 @@
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + Met_bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + BW_frac_Mat</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + Met_bw_kg + adg_kg_day + milk_prod_kg_d + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2221, 2224)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 229, 230, 231, 233, 234, 235, 236, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2137, 2138, 2139, 2194, 2222, 2223, 2225, 2226, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">c(222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1728, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 1965, 2027, 2031, 2119, 2120, 2121, 2123, 2124, 2125, 2126, 2127)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 223, 225, 227, 243, 244, 245, 246, 247, 248, 249, 250, 269, 270, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1812, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1935, 1990, 1991, 1992, 1993, 2026, 2030, 2107, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2194, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + Ash_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(41, 42, 43, 44, 222, 224, 226, 228, 275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 2027, 2119, 2120, 2121, 2124, 2125, 2126, 2127, 2221, 2224)</t>
+    <t xml:space="preserve">c(20, 21, 22, 23, 1652, 1653, 1654, 1655, 1690, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1824, 1825, 1826, 1827, 1897, 1898, 1900, 2054, 2055, 2056, 2058, 2177, 2179, 2279, 2281, 2282, 2283, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2108, 2109, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 
-2194, 2222, 2223, 2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + Ash_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + EE_nutrition</t>
+    <t xml:space="preserve">c(275, 276, 277, 278, 279, 280, 1719, 1720, 1721, 1722, 1727, 1728, 1775, 1776, 1777, 1778, 1779, 1868, 1869, 1870, 1965, 2027, 2031, 2119, 2120, 2121, 2123, 2124, 2125, 2126, 2127)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(17, 18, 19, 20, 23, 31, 32, 33, 34, 35, 1691, 1692, 1693, 1750, 1751, 1752, 1753, 1754, 1755, 1756, 1757, 1771, 1772, 1773, 1774, 1824, 1825, 1826, 1827, 2054, 2056, 2058, 2177, 2179, 2288, 2289, 2290, 2292, 2293, 2294, 2295)</t>
+    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 175, 177, 180, 243, 244, 245, 246, 269, 270, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1764, 1765, 1766, 1812, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1990, 1991, 1992, 1993, 2026, 2030, 2107, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2194, 2257, 2300, 2301, 2302, 2303)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(13, 15, 70, 71, 72, 73, 130, 131, 132, 140, 141, 142, 143, 177, 221, 223, 225, 227, 229, 230, 231, 233, 234, 235, 236, 243, 244, 245, 246, 247, 248, 249, 250, 271, 272, 273, 274, 281, 282, 283, 284, 285, 286, 287, 288, 289, 290, 291, 292, 293, 294, 295, 296, 1716, 1717, 1718, 1760, 1761, 1762, 1763, 1764, 1765, 1766, 1838, 1839, 1840, 1852, 1863, 1864, 1865, 1866, 1867, 1935, 1990, 1991, 1992, 2026, 2030, 2128, 2129, 2130, 2131, 2132, 2133, 2134, 2135, 2136, 2137, 2138, 2139, 2194, 2222, 2223, 
-2225, 2226, 2257, 2300, 2301, 2302, 2303, 2312, 2313)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(70, 71, 72, 73, 175, 177, 180, 269, 270, 271, 272, 273, 274, 1764, 1765, 1766, 1935)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + Ash_nutrition.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + Ash_nutrition.cbd + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + NDF_nutrition.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + EE_nutrition.cbd + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + CP_nutrition.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + NDF_nutrition.cbd + milk_prod_kg_d</t>
   </si>
 </sst>
 </file>
@@ -596,13 +615,13 @@
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q2" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3">
@@ -649,13 +668,13 @@
         <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q3" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
@@ -702,13 +721,13 @@
         <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q4" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
@@ -755,13 +774,13 @@
         <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6">
@@ -808,13 +827,13 @@
         <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q6" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
@@ -861,13 +880,13 @@
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q7" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
@@ -914,13 +933,13 @@
         <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9">
@@ -967,13 +986,13 @@
         <v>29</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -1020,13 +1039,13 @@
         <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -1073,13 +1092,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P11" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q11" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12">
@@ -1126,13 +1145,13 @@
         <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P12" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q12" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13">
@@ -1179,13 +1198,13 @@
         <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P13" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q13" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="14">
@@ -1232,13 +1251,13 @@
         <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q14" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15">
@@ -1285,13 +1304,13 @@
         <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q15" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16">
@@ -1338,13 +1357,13 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q16" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17">
@@ -1391,13 +1410,13 @@
         <v>26</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q17" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
@@ -1444,13 +1463,13 @@
         <v>26</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P18" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q18" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
@@ -1497,13 +1516,13 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q19" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20">
@@ -1550,13 +1569,13 @@
         <v>29</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q20" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
@@ -1603,13 +1622,13 @@
         <v>29</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
@@ -1656,13 +1675,13 @@
         <v>29</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23">
@@ -1709,13 +1728,13 @@
         <v>32</v>
       </c>
       <c r="O23" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P23" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q23" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="24">
@@ -1762,13 +1781,13 @@
         <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P24" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q24" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="25">
@@ -1815,13 +1834,13 @@
         <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P25" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q25" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="26">
@@ -1868,13 +1887,13 @@
         <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q26" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27">
@@ -1921,13 +1940,13 @@
         <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q27" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28">
@@ -1974,13 +1993,13 @@
         <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q28" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29">
@@ -2015,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2027,13 +2046,13 @@
         <v>26</v>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P29" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q29" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30">
@@ -2068,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2080,13 +2099,13 @@
         <v>26</v>
       </c>
       <c r="O30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P30" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q30" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31">
@@ -2121,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -2133,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P31" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q31" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32">
@@ -2186,13 +2205,13 @@
         <v>29</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q32" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33">
@@ -2239,13 +2258,13 @@
         <v>29</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q33" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34">
@@ -2292,13 +2311,13 @@
         <v>29</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q34" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35">
@@ -2333,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2345,13 +2364,13 @@
         <v>32</v>
       </c>
       <c r="O35" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P35" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q35" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36">
@@ -2386,7 +2405,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2398,13 +2417,13 @@
         <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P36" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q36" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="37">
@@ -2439,7 +2458,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -2451,13 +2470,13 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P37" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q37" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="38">
@@ -2504,13 +2523,13 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q38" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39">
@@ -2557,13 +2576,13 @@
         <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q39" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40">
@@ -2610,13 +2629,13 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q40" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41">
@@ -2651,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2663,13 +2682,13 @@
         <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P41" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q41" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42">
@@ -2704,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2716,13 +2735,13 @@
         <v>26</v>
       </c>
       <c r="O42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P42" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q42" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43">
@@ -2757,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -2769,13 +2788,13 @@
         <v>26</v>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q43" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44">
@@ -2822,13 +2841,13 @@
         <v>29</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q44" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45">
@@ -2875,13 +2894,13 @@
         <v>29</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q45" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46">
@@ -2928,13 +2947,13 @@
         <v>29</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q46" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47">
@@ -2969,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2981,13 +3000,13 @@
         <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P47" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q47" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="48">
@@ -3022,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3034,13 +3053,13 @@
         <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P48" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q48" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="49">
@@ -3075,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -3087,13 +3106,13 @@
         <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P49" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q49" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="50">
@@ -3128,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3140,13 +3159,13 @@
         <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q50" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51">
@@ -3181,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3193,13 +3212,13 @@
         <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P51" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q51" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52">
@@ -3234,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3246,13 +3265,13 @@
         <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q52" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53">
@@ -3287,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3299,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P53" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q53" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54">
@@ -3340,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3352,13 +3371,13 @@
         <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q54" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55">
@@ -3393,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3405,13 +3424,13 @@
         <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P55" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q55" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56">
@@ -3446,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3458,13 +3477,13 @@
         <v>29</v>
       </c>
       <c r="O56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q56" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
@@ -3499,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3511,13 +3530,13 @@
         <v>29</v>
       </c>
       <c r="O57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q57" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58">
@@ -3552,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3564,13 +3583,13 @@
         <v>29</v>
       </c>
       <c r="O58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q58" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59">
@@ -3605,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3617,13 +3636,13 @@
         <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P59" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q59" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="60">
@@ -3658,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3670,13 +3689,13 @@
         <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P60" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q60" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="61">
@@ -3711,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3723,13 +3742,13 @@
         <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P61" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q61" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="62">
@@ -3764,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3776,13 +3795,13 @@
         <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q62" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63">
@@ -3817,7 +3836,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3829,13 +3848,13 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q63" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64">
@@ -3870,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3882,13 +3901,13 @@
         <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P64" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q64" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65">
@@ -3923,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3935,13 +3954,13 @@
         <v>26</v>
       </c>
       <c r="O65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P65" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q65" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66">
@@ -3976,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -3988,13 +4007,13 @@
         <v>26</v>
       </c>
       <c r="O66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P66" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q66" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67">
@@ -4029,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4041,13 +4060,13 @@
         <v>26</v>
       </c>
       <c r="O67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P67" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q67" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68">
@@ -4082,7 +4101,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4094,13 +4113,13 @@
         <v>29</v>
       </c>
       <c r="O68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P68" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q68" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69">
@@ -4135,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4147,13 +4166,13 @@
         <v>29</v>
       </c>
       <c r="O69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P69" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70">
@@ -4188,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4200,13 +4219,13 @@
         <v>29</v>
       </c>
       <c r="O70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P70" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q70" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71">
@@ -4241,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4253,13 +4272,13 @@
         <v>32</v>
       </c>
       <c r="O71" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P71" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q71" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="72">
@@ -4294,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4306,13 +4325,13 @@
         <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P72" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q72" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="73">
@@ -4347,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4359,13 +4378,13 @@
         <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P73" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="Q73" t="n">
-        <v>811</v>
+        <v>656</v>
       </c>
     </row>
     <row r="74">
@@ -4400,7 +4419,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4412,13 +4431,13 @@
         <v>22</v>
       </c>
       <c r="O74" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q74" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75">
@@ -4453,7 +4472,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4465,13 +4484,13 @@
         <v>22</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q75" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76">
@@ -4506,7 +4525,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4518,13 +4537,13 @@
         <v>22</v>
       </c>
       <c r="O76" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q76" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77">
@@ -4559,25 +4578,25 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
       </c>
       <c r="O77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P77" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q77" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78">
@@ -4612,25 +4631,25 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P78" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q78" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79">
@@ -4665,25 +4684,25 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
       </c>
       <c r="O79" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P79" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q79" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80">
@@ -4718,7 +4737,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4730,13 +4749,13 @@
         <v>29</v>
       </c>
       <c r="O80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q80" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81">
@@ -4771,7 +4790,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4783,13 +4802,13 @@
         <v>29</v>
       </c>
       <c r="O81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q81" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82">
@@ -4824,7 +4843,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4836,13 +4855,13 @@
         <v>29</v>
       </c>
       <c r="O82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P82" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q82" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83">
@@ -4877,25 +4896,25 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N83" t="s">
         <v>32</v>
       </c>
       <c r="O83" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P83" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="Q83" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84">
@@ -4930,25 +4949,25 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N84" t="s">
         <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P84" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="Q84" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85">
@@ -4983,25 +5002,25 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N85" t="s">
         <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P85" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="Q85" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="86">
@@ -5036,7 +5055,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5048,13 +5067,13 @@
         <v>22</v>
       </c>
       <c r="O86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P86" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q86" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="87">
@@ -5089,7 +5108,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5101,13 +5120,13 @@
         <v>22</v>
       </c>
       <c r="O87" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q87" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88">
@@ -5142,7 +5161,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5154,13 +5173,13 @@
         <v>22</v>
       </c>
       <c r="O88" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P88" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="Q88" t="n">
-        <v>395</v>
+        <v>294</v>
       </c>
     </row>
     <row r="89">
@@ -5195,25 +5214,25 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
       </c>
       <c r="O89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P89" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90">
@@ -5248,25 +5267,25 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
       </c>
       <c r="O90" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P90" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q90" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91">
@@ -5301,25 +5320,25 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
       </c>
       <c r="O91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P91" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q91" t="n">
-        <v>79</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92">
@@ -5354,7 +5373,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5366,13 +5385,13 @@
         <v>29</v>
       </c>
       <c r="O92" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q92" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93">
@@ -5407,7 +5426,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5419,13 +5438,13 @@
         <v>29</v>
       </c>
       <c r="O93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q93" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94">
@@ -5460,7 +5479,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5472,13 +5491,13 @@
         <v>29</v>
       </c>
       <c r="O94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P94" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q94" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95">
@@ -5513,25 +5532,25 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N95" t="s">
         <v>32</v>
       </c>
       <c r="O95" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P95" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="Q95" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="96">
@@ -5566,25 +5585,25 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N96" t="s">
         <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P96" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="Q96" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="97">
@@ -5619,25 +5638,25 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N97" t="s">
         <v>32</v>
       </c>
       <c r="O97" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P97" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="Q97" t="n">
-        <v>489</v>
+        <v>547</v>
       </c>
     </row>
     <row r="98">
@@ -5672,25 +5691,25 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N98" t="s">
         <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P98" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q98" t="n">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99">
@@ -5725,25 +5744,25 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N99" t="s">
         <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P99" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q99" t="n">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100">
@@ -5778,25 +5797,25 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N100" t="s">
         <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P100" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q100" t="n">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101">
@@ -5831,25 +5850,25 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N101" t="s">
         <v>26</v>
       </c>
       <c r="O101" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P101" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q101" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102">
@@ -5884,25 +5903,25 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N102" t="s">
         <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P102" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q102" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103">
@@ -5937,25 +5956,25 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N103" t="s">
         <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P103" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q103" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="104">
@@ -5990,7 +6009,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6002,13 +6021,13 @@
         <v>29</v>
       </c>
       <c r="O104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P104" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q104" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105">
@@ -6043,7 +6062,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6055,13 +6074,13 @@
         <v>29</v>
       </c>
       <c r="O105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P105" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q105" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="106">
@@ -6096,7 +6115,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6108,13 +6127,13 @@
         <v>29</v>
       </c>
       <c r="O106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P106" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q106" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107">
@@ -6149,25 +6168,25 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
       </c>
       <c r="O107" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P107" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q107" t="n">
-        <v>728</v>
+        <v>454</v>
       </c>
     </row>
     <row r="108">
@@ -6202,25 +6221,25 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P108" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q108" t="n">
-        <v>728</v>
+        <v>454</v>
       </c>
     </row>
     <row r="109">
@@ -6255,25 +6274,25 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N109" t="s">
         <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P109" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q109" t="n">
-        <v>728</v>
+        <v>454</v>
       </c>
     </row>
     <row r="110">
@@ -6308,25 +6327,25 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N110" t="s">
         <v>22</v>
       </c>
       <c r="O110" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P110" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q110" t="n">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111">
@@ -6361,25 +6380,25 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N111" t="s">
         <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P111" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q111" t="n">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112">
@@ -6414,25 +6433,25 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="N112" t="s">
         <v>22</v>
       </c>
       <c r="O112" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P112" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Q112" t="n">
-        <v>395</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113">
@@ -6467,25 +6486,25 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N113" t="s">
         <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P113" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q113" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="114">
@@ -6520,25 +6539,25 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N114" t="s">
         <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P114" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q114" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="115">
@@ -6573,25 +6592,25 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N115" t="s">
         <v>26</v>
       </c>
       <c r="O115" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P115" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q115" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116">
@@ -6626,7 +6645,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6638,13 +6657,13 @@
         <v>29</v>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P116" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q116" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="117">
@@ -6679,7 +6698,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6691,13 +6710,13 @@
         <v>29</v>
       </c>
       <c r="O117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q117" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="118">
@@ -6732,7 +6751,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6744,13 +6763,13 @@
         <v>29</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P118" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q118" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="119">
@@ -6785,25 +6804,25 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
       </c>
       <c r="O119" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P119" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q119" t="n">
-        <v>728</v>
+        <v>454</v>
       </c>
     </row>
     <row r="120">
@@ -6838,25 +6857,25 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
       </c>
       <c r="O120" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P120" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q120" t="n">
-        <v>728</v>
+        <v>454</v>
       </c>
     </row>
     <row r="121">
@@ -6891,25 +6910,25 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
       </c>
       <c r="O121" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="P121" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="Q121" t="n">
-        <v>728</v>
+        <v>454</v>
       </c>
     </row>
     <row r="122">
@@ -6944,25 +6963,25 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P122" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q122" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123">
@@ -6997,25 +7016,25 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P123" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q123" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="124">
@@ -7050,25 +7069,25 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P124" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q124" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125">
@@ -7076,7 +7095,7 @@
         <v>250</v>
       </c>
       <c r="B125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" t="s">
         <v>17</v>
@@ -7103,33 +7122,29 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N125" t="s">
         <v>26</v>
       </c>
-      <c r="O125" t="n">
-        <v>10</v>
-      </c>
+      <c r="O125"/>
       <c r="P125" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q125"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>251</v>
       </c>
       <c r="B126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126" t="s">
         <v>17</v>
@@ -7156,33 +7171,29 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N126" t="s">
         <v>26</v>
       </c>
-      <c r="O126" t="n">
-        <v>10</v>
-      </c>
+      <c r="O126"/>
       <c r="P126" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q126"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>252</v>
       </c>
       <c r="B127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127" t="s">
         <v>17</v>
@@ -7209,33 +7220,29 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N127" t="s">
         <v>26</v>
       </c>
-      <c r="O127" t="n">
-        <v>10</v>
-      </c>
+      <c r="O127"/>
       <c r="P127" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q127"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>256</v>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="s">
         <v>17</v>
@@ -7262,7 +7269,7 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -7273,18 +7280,22 @@
       <c r="N128" t="s">
         <v>29</v>
       </c>
-      <c r="O128"/>
+      <c r="O128" t="n">
+        <v>5</v>
+      </c>
       <c r="P128" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q128"/>
+        <v>24</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>257</v>
       </c>
       <c r="B129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" t="s">
         <v>17</v>
@@ -7311,7 +7322,7 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
@@ -7322,18 +7333,22 @@
       <c r="N129" t="s">
         <v>29</v>
       </c>
-      <c r="O129"/>
+      <c r="O129" t="n">
+        <v>5</v>
+      </c>
       <c r="P129" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q129"/>
+        <v>24</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>258</v>
       </c>
       <c r="B130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130" t="s">
         <v>17</v>
@@ -7360,7 +7375,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7371,11 +7386,15 @@
       <c r="N130" t="s">
         <v>29</v>
       </c>
-      <c r="O130"/>
+      <c r="O130" t="n">
+        <v>5</v>
+      </c>
       <c r="P130" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q130"/>
+        <v>24</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7409,25 +7428,25 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N131" t="s">
         <v>32</v>
       </c>
       <c r="O131" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="P131" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="Q131" t="n">
-        <v>702</v>
+        <v>101</v>
       </c>
     </row>
     <row r="132">
@@ -7462,25 +7481,25 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N132" t="s">
         <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="P132" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="Q132" t="n">
-        <v>702</v>
+        <v>101</v>
       </c>
     </row>
     <row r="133">
@@ -7515,25 +7534,25 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N133" t="s">
         <v>32</v>
       </c>
       <c r="O133" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="P133" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="Q133" t="n">
-        <v>702</v>
+        <v>101</v>
       </c>
     </row>
     <row r="134">
@@ -7568,25 +7587,25 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P134" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q134" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="135">
@@ -7621,25 +7640,25 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P135" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q135" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="136">
@@ -7674,25 +7693,25 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P136" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="Q136" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="137">
@@ -7700,7 +7719,7 @@
         <v>274</v>
       </c>
       <c r="B137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" t="s">
         <v>17</v>
@@ -7727,33 +7746,29 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N137" t="s">
         <v>26</v>
       </c>
-      <c r="O137" t="n">
-        <v>10</v>
-      </c>
+      <c r="O137"/>
       <c r="P137" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q137"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>275</v>
       </c>
       <c r="B138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" t="s">
         <v>17</v>
@@ -7780,33 +7795,29 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N138" t="s">
         <v>26</v>
       </c>
-      <c r="O138" t="n">
-        <v>10</v>
-      </c>
+      <c r="O138"/>
       <c r="P138" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q138"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>276</v>
       </c>
       <c r="B139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" t="s">
         <v>17</v>
@@ -7833,33 +7844,29 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N139" t="s">
         <v>26</v>
       </c>
-      <c r="O139" t="n">
-        <v>10</v>
-      </c>
+      <c r="O139"/>
       <c r="P139" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="Q139"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>280</v>
       </c>
       <c r="B140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -7886,7 +7893,7 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
@@ -7897,18 +7904,22 @@
       <c r="N140" t="s">
         <v>29</v>
       </c>
-      <c r="O140"/>
+      <c r="O140" t="n">
+        <v>5</v>
+      </c>
       <c r="P140" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q140"/>
+        <v>24</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>281</v>
       </c>
       <c r="B141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -7935,7 +7946,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
@@ -7946,18 +7957,22 @@
       <c r="N141" t="s">
         <v>29</v>
       </c>
-      <c r="O141"/>
+      <c r="O141" t="n">
+        <v>5</v>
+      </c>
       <c r="P141" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q141"/>
+        <v>24</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>282</v>
       </c>
       <c r="B142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -7984,7 +7999,7 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
@@ -7995,11 +8010,15 @@
       <c r="N142" t="s">
         <v>29</v>
       </c>
-      <c r="O142"/>
+      <c r="O142" t="n">
+        <v>5</v>
+      </c>
       <c r="P142" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q142"/>
+        <v>24</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8033,25 +8052,25 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N143" t="s">
         <v>32</v>
       </c>
       <c r="O143" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="P143" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="Q143" t="n">
-        <v>702</v>
+        <v>101</v>
       </c>
     </row>
     <row r="144">
@@ -8086,25 +8105,25 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N144" t="s">
         <v>32</v>
       </c>
       <c r="O144" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="P144" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="Q144" t="n">
-        <v>702</v>
+        <v>101</v>
       </c>
     </row>
     <row r="145">
@@ -8139,25 +8158,3817 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N145" t="s">
         <v>32</v>
       </c>
       <c r="O145" t="n">
+        <v>5</v>
+      </c>
+      <c r="P145" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>292</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="s">
+        <v>53</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="s">
+        <v>46</v>
+      </c>
+      <c r="N146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O146" t="n">
+        <v>11</v>
+      </c>
+      <c r="P146" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>293</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>53</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>46</v>
+      </c>
+      <c r="N147" t="s">
+        <v>22</v>
+      </c>
+      <c r="O147" t="n">
+        <v>11</v>
+      </c>
+      <c r="P147" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>294</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>53</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="s">
+        <v>46</v>
+      </c>
+      <c r="N148" t="s">
+        <v>22</v>
+      </c>
+      <c r="O148" t="n">
+        <v>11</v>
+      </c>
+      <c r="P148" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>298</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>54</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>48</v>
+      </c>
+      <c r="N149" t="s">
+        <v>26</v>
+      </c>
+      <c r="O149" t="n">
+        <v>8</v>
+      </c>
+      <c r="P149" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>299</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>54</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="s">
+        <v>48</v>
+      </c>
+      <c r="N150" t="s">
+        <v>26</v>
+      </c>
+      <c r="O150" t="n">
+        <v>8</v>
+      </c>
+      <c r="P150" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>300</v>
+      </c>
+      <c r="B151" t="b">
+        <v>0</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>54</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="s">
+        <v>48</v>
+      </c>
+      <c r="N151" t="s">
+        <v>26</v>
+      </c>
+      <c r="O151" t="n">
+        <v>8</v>
+      </c>
+      <c r="P151" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>304</v>
+      </c>
+      <c r="B152" t="b">
+        <v>0</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" t="n">
+        <v>7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>53</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="s">
+        <v>28</v>
+      </c>
+      <c r="N152" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152" t="n">
+        <v>5</v>
+      </c>
+      <c r="P152" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>305</v>
+      </c>
+      <c r="B153" t="b">
+        <v>0</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I153" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>53</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" t="s">
+        <v>29</v>
+      </c>
+      <c r="O153" t="n">
+        <v>5</v>
+      </c>
+      <c r="P153" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>306</v>
+      </c>
+      <c r="B154" t="b">
+        <v>0</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>53</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O154" t="n">
+        <v>5</v>
+      </c>
+      <c r="P154" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>310</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
         <v>30</v>
       </c>
-      <c r="P145" t="n">
-        <v>102</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>702</v>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>54</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="s">
+        <v>49</v>
+      </c>
+      <c r="N155" t="s">
+        <v>32</v>
+      </c>
+      <c r="O155" t="n">
+        <v>21</v>
+      </c>
+      <c r="P155" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>311</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>30</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>54</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="s">
+        <v>49</v>
+      </c>
+      <c r="N156" t="s">
+        <v>32</v>
+      </c>
+      <c r="O156" t="n">
+        <v>21</v>
+      </c>
+      <c r="P156" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>312</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>30</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>54</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" t="s">
+        <v>49</v>
+      </c>
+      <c r="N157" t="s">
+        <v>32</v>
+      </c>
+      <c r="O157" t="n">
+        <v>21</v>
+      </c>
+      <c r="P157" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>316</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="s">
+        <v>33</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="s">
+        <v>53</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>46</v>
+      </c>
+      <c r="N158" t="s">
+        <v>22</v>
+      </c>
+      <c r="O158" t="n">
+        <v>11</v>
+      </c>
+      <c r="P158" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>317</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="s">
+        <v>33</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>53</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="s">
+        <v>46</v>
+      </c>
+      <c r="N159" t="s">
+        <v>22</v>
+      </c>
+      <c r="O159" t="n">
+        <v>11</v>
+      </c>
+      <c r="P159" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>318</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>33</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>53</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="s">
+        <v>46</v>
+      </c>
+      <c r="N160" t="s">
+        <v>22</v>
+      </c>
+      <c r="O160" t="n">
+        <v>11</v>
+      </c>
+      <c r="P160" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>322</v>
+      </c>
+      <c r="B161" t="b">
+        <v>0</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>54</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="s">
+        <v>48</v>
+      </c>
+      <c r="N161" t="s">
+        <v>26</v>
+      </c>
+      <c r="O161" t="n">
+        <v>8</v>
+      </c>
+      <c r="P161" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>323</v>
+      </c>
+      <c r="B162" t="b">
+        <v>0</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>34</v>
+      </c>
+      <c r="I162" t="n">
+        <v>7</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>54</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="s">
+        <v>48</v>
+      </c>
+      <c r="N162" t="s">
+        <v>26</v>
+      </c>
+      <c r="O162" t="n">
+        <v>8</v>
+      </c>
+      <c r="P162" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>324</v>
+      </c>
+      <c r="B163" t="b">
+        <v>0</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="s">
+        <v>34</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>54</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="s">
+        <v>48</v>
+      </c>
+      <c r="N163" t="s">
+        <v>26</v>
+      </c>
+      <c r="O163" t="n">
+        <v>8</v>
+      </c>
+      <c r="P163" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>328</v>
+      </c>
+      <c r="B164" t="b">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="s">
+        <v>35</v>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="s">
+        <v>53</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" t="s">
+        <v>29</v>
+      </c>
+      <c r="O164" t="n">
+        <v>5</v>
+      </c>
+      <c r="P164" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>329</v>
+      </c>
+      <c r="B165" t="b">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="s">
+        <v>35</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="s">
+        <v>53</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" t="s">
+        <v>29</v>
+      </c>
+      <c r="O165" t="n">
+        <v>5</v>
+      </c>
+      <c r="P165" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>330</v>
+      </c>
+      <c r="B166" t="b">
+        <v>0</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="s">
+        <v>35</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
+        <v>53</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" t="s">
+        <v>28</v>
+      </c>
+      <c r="N166" t="s">
+        <v>29</v>
+      </c>
+      <c r="O166" t="n">
+        <v>5</v>
+      </c>
+      <c r="P166" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>334</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="s">
+        <v>36</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="s">
+        <v>54</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="s">
+        <v>49</v>
+      </c>
+      <c r="N167" t="s">
+        <v>32</v>
+      </c>
+      <c r="O167" t="n">
+        <v>21</v>
+      </c>
+      <c r="P167" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>335</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
+        <v>36</v>
+      </c>
+      <c r="I168" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="s">
+        <v>54</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="s">
+        <v>49</v>
+      </c>
+      <c r="N168" t="s">
+        <v>32</v>
+      </c>
+      <c r="O168" t="n">
+        <v>21</v>
+      </c>
+      <c r="P168" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>336</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="s">
+        <v>36</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="s">
+        <v>54</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="s">
+        <v>49</v>
+      </c>
+      <c r="N169" t="s">
+        <v>32</v>
+      </c>
+      <c r="O169" t="n">
+        <v>21</v>
+      </c>
+      <c r="P169" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>340</v>
+      </c>
+      <c r="B170" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>19</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="s">
+        <v>55</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="s">
+        <v>21</v>
+      </c>
+      <c r="N170" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" t="n">
+        <v>12</v>
+      </c>
+      <c r="P170" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>341</v>
+      </c>
+      <c r="B171" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>55</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="s">
+        <v>21</v>
+      </c>
+      <c r="N171" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" t="n">
+        <v>12</v>
+      </c>
+      <c r="P171" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>342</v>
+      </c>
+      <c r="B172" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="s">
+        <v>55</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="s">
+        <v>21</v>
+      </c>
+      <c r="N172" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" t="n">
+        <v>12</v>
+      </c>
+      <c r="P172" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>346</v>
+      </c>
+      <c r="B173" t="b">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="s">
+        <v>56</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="s">
+        <v>25</v>
+      </c>
+      <c r="N173" t="s">
+        <v>26</v>
+      </c>
+      <c r="O173"/>
+      <c r="P173" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q173"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>347</v>
+      </c>
+      <c r="B174" t="b">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="s">
+        <v>56</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="s">
+        <v>25</v>
+      </c>
+      <c r="N174" t="s">
+        <v>26</v>
+      </c>
+      <c r="O174"/>
+      <c r="P174" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q174"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>348</v>
+      </c>
+      <c r="B175" t="b">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>18</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>56</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="s">
+        <v>25</v>
+      </c>
+      <c r="N175" t="s">
+        <v>26</v>
+      </c>
+      <c r="O175"/>
+      <c r="P175" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q175"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>352</v>
+      </c>
+      <c r="B176" t="b">
+        <v>0</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>27</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>55</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O176" t="n">
+        <v>5</v>
+      </c>
+      <c r="P176" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>353</v>
+      </c>
+      <c r="B177" t="b">
+        <v>0</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>18</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="s">
+        <v>27</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>55</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177" t="n">
+        <v>5</v>
+      </c>
+      <c r="P177" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>354</v>
+      </c>
+      <c r="B178" t="b">
+        <v>0</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>27</v>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="s">
+        <v>55</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="s">
+        <v>28</v>
+      </c>
+      <c r="N178" t="s">
+        <v>29</v>
+      </c>
+      <c r="O178" t="n">
+        <v>5</v>
+      </c>
+      <c r="P178" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>358</v>
+      </c>
+      <c r="B179" t="b">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>30</v>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="s">
+        <v>56</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="s">
+        <v>52</v>
+      </c>
+      <c r="N179" t="s">
+        <v>32</v>
+      </c>
+      <c r="O179" t="n">
+        <v>5</v>
+      </c>
+      <c r="P179" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>359</v>
+      </c>
+      <c r="B180" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>18</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>30</v>
+      </c>
+      <c r="I180" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="s">
+        <v>56</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="s">
+        <v>52</v>
+      </c>
+      <c r="N180" t="s">
+        <v>32</v>
+      </c>
+      <c r="O180" t="n">
+        <v>5</v>
+      </c>
+      <c r="P180" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>360</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>18</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>30</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="s">
+        <v>56</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="s">
+        <v>52</v>
+      </c>
+      <c r="N181" t="s">
+        <v>32</v>
+      </c>
+      <c r="O181" t="n">
+        <v>5</v>
+      </c>
+      <c r="P181" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>364</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>33</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="s">
+        <v>55</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
+        <v>21</v>
+      </c>
+      <c r="N182" t="s">
+        <v>22</v>
+      </c>
+      <c r="O182" t="n">
+        <v>12</v>
+      </c>
+      <c r="P182" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>365</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>33</v>
+      </c>
+      <c r="I183" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="s">
+        <v>55</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>21</v>
+      </c>
+      <c r="N183" t="s">
+        <v>22</v>
+      </c>
+      <c r="O183" t="n">
+        <v>12</v>
+      </c>
+      <c r="P183" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>366</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>33</v>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="s">
+        <v>55</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>21</v>
+      </c>
+      <c r="N184" t="s">
+        <v>22</v>
+      </c>
+      <c r="O184" t="n">
+        <v>12</v>
+      </c>
+      <c r="P184" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>370</v>
+      </c>
+      <c r="B185" t="b">
+        <v>1</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>34</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="s">
+        <v>56</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="s">
+        <v>25</v>
+      </c>
+      <c r="N185" t="s">
+        <v>26</v>
+      </c>
+      <c r="O185"/>
+      <c r="P185" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q185"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>371</v>
+      </c>
+      <c r="B186" t="b">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="s">
+        <v>34</v>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>56</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="s">
+        <v>25</v>
+      </c>
+      <c r="N186" t="s">
+        <v>26</v>
+      </c>
+      <c r="O186"/>
+      <c r="P186" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>372</v>
+      </c>
+      <c r="B187" t="b">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="s">
+        <v>34</v>
+      </c>
+      <c r="I187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>56</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="s">
+        <v>25</v>
+      </c>
+      <c r="N187" t="s">
+        <v>26</v>
+      </c>
+      <c r="O187"/>
+      <c r="P187" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>376</v>
+      </c>
+      <c r="B188" t="b">
+        <v>0</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="s">
+        <v>35</v>
+      </c>
+      <c r="I188" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="s">
+        <v>55</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188" t="s">
+        <v>29</v>
+      </c>
+      <c r="O188" t="n">
+        <v>5</v>
+      </c>
+      <c r="P188" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>377</v>
+      </c>
+      <c r="B189" t="b">
+        <v>0</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="s">
+        <v>35</v>
+      </c>
+      <c r="I189" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="s">
+        <v>55</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
+        <v>29</v>
+      </c>
+      <c r="O189" t="n">
+        <v>5</v>
+      </c>
+      <c r="P189" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>378</v>
+      </c>
+      <c r="B190" t="b">
+        <v>0</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="s">
+        <v>35</v>
+      </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="s">
+        <v>55</v>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="s">
+        <v>28</v>
+      </c>
+      <c r="N190" t="s">
+        <v>29</v>
+      </c>
+      <c r="O190" t="n">
+        <v>5</v>
+      </c>
+      <c r="P190" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>382</v>
+      </c>
+      <c r="B191" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="s">
+        <v>36</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="s">
+        <v>56</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="s">
+        <v>52</v>
+      </c>
+      <c r="N191" t="s">
+        <v>32</v>
+      </c>
+      <c r="O191" t="n">
+        <v>5</v>
+      </c>
+      <c r="P191" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>383</v>
+      </c>
+      <c r="B192" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="s">
+        <v>36</v>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="s">
+        <v>56</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="s">
+        <v>52</v>
+      </c>
+      <c r="N192" t="s">
+        <v>32</v>
+      </c>
+      <c r="O192" t="n">
+        <v>5</v>
+      </c>
+      <c r="P192" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>384</v>
+      </c>
+      <c r="B193" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="s">
+        <v>36</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>56</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>52</v>
+      </c>
+      <c r="N193" t="s">
+        <v>32</v>
+      </c>
+      <c r="O193" t="n">
+        <v>5</v>
+      </c>
+      <c r="P193" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>388</v>
+      </c>
+      <c r="B194" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" t="n">
+        <v>9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>57</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>21</v>
+      </c>
+      <c r="N194" t="s">
+        <v>22</v>
+      </c>
+      <c r="O194" t="n">
+        <v>12</v>
+      </c>
+      <c r="P194" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>389</v>
+      </c>
+      <c r="B195" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>57</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="s">
+        <v>21</v>
+      </c>
+      <c r="N195" t="s">
+        <v>22</v>
+      </c>
+      <c r="O195" t="n">
+        <v>12</v>
+      </c>
+      <c r="P195" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>390</v>
+      </c>
+      <c r="B196" t="b">
+        <v>0</v>
+      </c>
+      <c r="C196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="s">
+        <v>57</v>
+      </c>
+      <c r="L196" t="n">
+        <v>3</v>
+      </c>
+      <c r="M196" t="s">
+        <v>21</v>
+      </c>
+      <c r="N196" t="s">
+        <v>22</v>
+      </c>
+      <c r="O196" t="n">
+        <v>12</v>
+      </c>
+      <c r="P196" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>394</v>
+      </c>
+      <c r="B197" t="b">
+        <v>0</v>
+      </c>
+      <c r="C197" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="s">
+        <v>58</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="s">
+        <v>43</v>
+      </c>
+      <c r="N197" t="s">
+        <v>26</v>
+      </c>
+      <c r="O197" t="n">
+        <v>9</v>
+      </c>
+      <c r="P197" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>395</v>
+      </c>
+      <c r="B198" t="b">
+        <v>0</v>
+      </c>
+      <c r="C198" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="s">
+        <v>58</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="s">
+        <v>43</v>
+      </c>
+      <c r="N198" t="s">
+        <v>26</v>
+      </c>
+      <c r="O198" t="n">
+        <v>9</v>
+      </c>
+      <c r="P198" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>396</v>
+      </c>
+      <c r="B199" t="b">
+        <v>0</v>
+      </c>
+      <c r="C199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="s">
+        <v>58</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="s">
+        <v>43</v>
+      </c>
+      <c r="N199" t="s">
+        <v>26</v>
+      </c>
+      <c r="O199" t="n">
+        <v>9</v>
+      </c>
+      <c r="P199" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>400</v>
+      </c>
+      <c r="B200" t="b">
+        <v>0</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="s">
+        <v>27</v>
+      </c>
+      <c r="I200" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="s">
+        <v>57</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="s">
+        <v>28</v>
+      </c>
+      <c r="N200" t="s">
+        <v>29</v>
+      </c>
+      <c r="O200" t="n">
+        <v>5</v>
+      </c>
+      <c r="P200" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>401</v>
+      </c>
+      <c r="B201" t="b">
+        <v>0</v>
+      </c>
+      <c r="C201" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>57</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>28</v>
+      </c>
+      <c r="N201" t="s">
+        <v>29</v>
+      </c>
+      <c r="O201" t="n">
+        <v>5</v>
+      </c>
+      <c r="P201" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>402</v>
+      </c>
+      <c r="B202" t="b">
+        <v>0</v>
+      </c>
+      <c r="C202" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="s">
+        <v>27</v>
+      </c>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>57</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="s">
+        <v>28</v>
+      </c>
+      <c r="N202" t="s">
+        <v>29</v>
+      </c>
+      <c r="O202" t="n">
+        <v>5</v>
+      </c>
+      <c r="P202" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>406</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="s">
+        <v>30</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>58</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>44</v>
+      </c>
+      <c r="N203" t="s">
+        <v>32</v>
+      </c>
+      <c r="O203" t="n">
+        <v>26</v>
+      </c>
+      <c r="P203" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>407</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="s">
+        <v>30</v>
+      </c>
+      <c r="I204" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>58</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="s">
+        <v>44</v>
+      </c>
+      <c r="N204" t="s">
+        <v>32</v>
+      </c>
+      <c r="O204" t="n">
+        <v>26</v>
+      </c>
+      <c r="P204" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>408</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="s">
+        <v>30</v>
+      </c>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="s">
+        <v>58</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="s">
+        <v>44</v>
+      </c>
+      <c r="N205" t="s">
+        <v>32</v>
+      </c>
+      <c r="O205" t="n">
+        <v>26</v>
+      </c>
+      <c r="P205" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>412</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="s">
+        <v>33</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>57</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>21</v>
+      </c>
+      <c r="N206" t="s">
+        <v>22</v>
+      </c>
+      <c r="O206" t="n">
+        <v>12</v>
+      </c>
+      <c r="P206" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>413</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="s">
+        <v>33</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>57</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="s">
+        <v>21</v>
+      </c>
+      <c r="N207" t="s">
+        <v>22</v>
+      </c>
+      <c r="O207" t="n">
+        <v>12</v>
+      </c>
+      <c r="P207" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>414</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="s">
+        <v>33</v>
+      </c>
+      <c r="I208" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>57</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>21</v>
+      </c>
+      <c r="N208" t="s">
+        <v>22</v>
+      </c>
+      <c r="O208" t="n">
+        <v>12</v>
+      </c>
+      <c r="P208" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>418</v>
+      </c>
+      <c r="B209" t="b">
+        <v>0</v>
+      </c>
+      <c r="C209" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="s">
+        <v>34</v>
+      </c>
+      <c r="I209" t="n">
+        <v>9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>58</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>43</v>
+      </c>
+      <c r="N209" t="s">
+        <v>26</v>
+      </c>
+      <c r="O209" t="n">
+        <v>9</v>
+      </c>
+      <c r="P209" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>419</v>
+      </c>
+      <c r="B210" t="b">
+        <v>0</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>18</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="s">
+        <v>34</v>
+      </c>
+      <c r="I210" t="n">
+        <v>9</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="s">
+        <v>58</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="s">
+        <v>43</v>
+      </c>
+      <c r="N210" t="s">
+        <v>26</v>
+      </c>
+      <c r="O210" t="n">
+        <v>9</v>
+      </c>
+      <c r="P210" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>420</v>
+      </c>
+      <c r="B211" t="b">
+        <v>0</v>
+      </c>
+      <c r="C211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="s">
+        <v>34</v>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="s">
+        <v>58</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>43</v>
+      </c>
+      <c r="N211" t="s">
+        <v>26</v>
+      </c>
+      <c r="O211" t="n">
+        <v>9</v>
+      </c>
+      <c r="P211" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>424</v>
+      </c>
+      <c r="B212" t="b">
+        <v>0</v>
+      </c>
+      <c r="C212" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="s">
+        <v>35</v>
+      </c>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="s">
+        <v>57</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="s">
+        <v>28</v>
+      </c>
+      <c r="N212" t="s">
+        <v>29</v>
+      </c>
+      <c r="O212" t="n">
+        <v>5</v>
+      </c>
+      <c r="P212" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>425</v>
+      </c>
+      <c r="B213" t="b">
+        <v>0</v>
+      </c>
+      <c r="C213" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213" t="s">
+        <v>18</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="s">
+        <v>35</v>
+      </c>
+      <c r="I213" t="n">
+        <v>9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>57</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="s">
+        <v>28</v>
+      </c>
+      <c r="N213" t="s">
+        <v>29</v>
+      </c>
+      <c r="O213" t="n">
+        <v>5</v>
+      </c>
+      <c r="P213" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>426</v>
+      </c>
+      <c r="B214" t="b">
+        <v>0</v>
+      </c>
+      <c r="C214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="s">
+        <v>35</v>
+      </c>
+      <c r="I214" t="n">
+        <v>9</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>57</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="s">
+        <v>28</v>
+      </c>
+      <c r="N214" t="s">
+        <v>29</v>
+      </c>
+      <c r="O214" t="n">
+        <v>5</v>
+      </c>
+      <c r="P214" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>430</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="s">
+        <v>36</v>
+      </c>
+      <c r="I215" t="n">
+        <v>9</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>58</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="s">
+        <v>44</v>
+      </c>
+      <c r="N215" t="s">
+        <v>32</v>
+      </c>
+      <c r="O215" t="n">
+        <v>26</v>
+      </c>
+      <c r="P215" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>431</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" t="s">
+        <v>18</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="s">
+        <v>36</v>
+      </c>
+      <c r="I216" t="n">
+        <v>9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="s">
+        <v>58</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="s">
+        <v>44</v>
+      </c>
+      <c r="N216" t="s">
+        <v>32</v>
+      </c>
+      <c r="O216" t="n">
+        <v>26</v>
+      </c>
+      <c r="P216" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>432</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="s">
+        <v>36</v>
+      </c>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="s">
+        <v>58</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="s">
+        <v>44</v>
+      </c>
+      <c r="N217" t="s">
+        <v>32</v>
+      </c>
+      <c r="O217" t="n">
+        <v>26</v>
+      </c>
+      <c r="P217" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
